--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Porjects\HorseLuis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5AAF0-6DCC-40F8-828E-9CE26E0EB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364E7D07-101A-4478-91B4-7969C0CBC0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="18780" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -754,7 +754,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="182">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -1294,6 +1294,12 @@
   </si>
   <si>
     <t>TRYAR</t>
+  </si>
+  <si>
+    <t>Horse Argentina</t>
+  </si>
+  <si>
+    <t>O0012</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1310,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1503,7 +1509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1526,12 +1532,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1682,6 +1699,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2022,10 +2043,10 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10" style="8" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -2049,7 +2070,7 @@
     <col min="51" max="51" width="13.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" ht="45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -2216,7 +2237,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58">
       <c r="A2" s="5" t="s">
         <v>138</v>
       </c>
@@ -2323,40 +2344,40 @@
         <v>74</v>
       </c>
       <c r="AI2" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AJ2" s="23">
         <f t="shared" ref="AJ2:AJ33" si="6">+AI2+AH2</f>
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM2" s="23">
         <f t="shared" ref="AM2:AM33" si="7">+AJ2+AL2</f>
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AN2" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO2" s="23">
         <f t="shared" ref="AO2:AO33" si="8">+AM2+AN2</f>
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AP2" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AQ2" s="3">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="AR2" s="23">
-        <f>+AQ2+4</f>
-        <v>96</v>
+        <f>+AQ2+7</f>
+        <v>91</v>
       </c>
       <c r="AS2" s="23">
         <f t="shared" ref="AS2:AS33" si="9">+AR2+7+AT2</f>
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="AT2" s="23">
         <v>14</v>
@@ -2378,7 +2399,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -2541,7 +2562,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -2716,7 +2737,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58">
       <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
@@ -2888,7 +2909,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58">
       <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
@@ -3061,7 +3082,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -3236,7 +3257,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -3408,7 +3429,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -3428,7 +3449,7 @@
         <v>90016000</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -3582,7 +3603,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58">
       <c r="A10" s="5" t="s">
         <v>168</v>
       </c>
@@ -3744,7 +3765,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -3907,7 +3928,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -4074,7 +4095,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1">
       <c r="A13" s="5">
         <v>60</v>
       </c>
@@ -4247,7 +4268,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1">
       <c r="A14" s="5">
         <v>120</v>
       </c>
@@ -4420,7 +4441,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1">
       <c r="A15" s="5">
         <v>121</v>
       </c>
@@ -4593,7 +4614,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1">
       <c r="A16" s="5">
         <v>233</v>
       </c>
@@ -4766,7 +4787,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1">
       <c r="A17" s="5">
         <v>416</v>
       </c>
@@ -4939,7 +4960,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1">
       <c r="A18" s="5">
         <v>901</v>
       </c>
@@ -5112,7 +5133,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1">
       <c r="A19" s="5">
         <v>904</v>
       </c>
@@ -5285,7 +5306,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1">
       <c r="A20" s="5">
         <v>906</v>
       </c>
@@ -5458,7 +5479,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1">
       <c r="A21" s="5">
         <v>907</v>
       </c>
@@ -5631,7 +5652,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1">
       <c r="A22" s="5">
         <v>908</v>
       </c>
@@ -5803,7 +5824,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1">
       <c r="A23" s="5">
         <v>910</v>
       </c>
@@ -5977,7 +5998,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1">
       <c r="A24" s="5">
         <v>912</v>
       </c>
@@ -6150,7 +6171,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1">
       <c r="A25" s="5">
         <v>915</v>
       </c>
@@ -6322,7 +6343,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1">
       <c r="A26" s="5">
         <v>916</v>
       </c>
@@ -6495,7 +6516,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1">
       <c r="A27" s="5">
         <v>917</v>
       </c>
@@ -6668,7 +6689,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="5">
         <v>918</v>
       </c>
@@ -6841,7 +6862,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1">
       <c r="A29" s="5">
         <v>920</v>
       </c>
@@ -7014,7 +7035,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1">
       <c r="A30" s="5">
         <v>921</v>
       </c>
@@ -7187,7 +7208,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1">
       <c r="A31" s="5">
         <v>924</v>
       </c>
@@ -7360,7 +7381,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1">
       <c r="A32" s="5">
         <v>925</v>
       </c>
@@ -7533,7 +7554,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1">
       <c r="A33" s="5">
         <v>927</v>
       </c>
@@ -7706,7 +7727,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1">
       <c r="A34" s="5">
         <v>928</v>
       </c>
@@ -7879,7 +7900,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1">
       <c r="A35" s="5">
         <v>930</v>
       </c>
@@ -8051,7 +8072,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" ht="30" hidden="1">
       <c r="A36" s="5">
         <v>931</v>
       </c>
@@ -8224,7 +8245,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1">
       <c r="A37" s="5">
         <v>932</v>
       </c>
@@ -8397,7 +8418,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1">
       <c r="A38" s="5">
         <v>1039</v>
       </c>
@@ -8570,7 +8591,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1">
       <c r="A39" s="5">
         <v>1045</v>
       </c>
@@ -8743,7 +8764,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1">
       <c r="A40" s="5">
         <v>1084</v>
       </c>
@@ -8916,7 +8937,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1">
       <c r="A41" s="5">
         <v>752</v>
       </c>
@@ -9087,7 +9108,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1">
       <c r="A42" s="5">
         <v>761</v>
       </c>
@@ -9257,7 +9278,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1">
       <c r="A43" s="5">
         <v>888</v>
       </c>
@@ -9429,7 +9450,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1">
       <c r="A44" s="5">
         <v>1005</v>
       </c>
@@ -9601,7 +9622,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" hidden="1">
       <c r="A45" s="5">
         <v>1006</v>
       </c>
@@ -9773,7 +9794,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1">
       <c r="A46" s="5">
         <v>1007</v>
       </c>
@@ -9947,7 +9968,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1">
       <c r="A47" s="5">
         <v>1009</v>
       </c>
@@ -10119,7 +10140,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" hidden="1">
       <c r="A48" s="5">
         <v>1010</v>
       </c>
@@ -10291,7 +10312,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1">
       <c r="A49" s="5">
         <v>1012</v>
       </c>
@@ -10464,7 +10485,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1">
       <c r="A50" s="5">
         <v>1014</v>
       </c>
@@ -10636,7 +10657,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1">
       <c r="A51" s="5">
         <v>1015</v>
       </c>
@@ -10808,7 +10829,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" hidden="1">
       <c r="A52" s="5">
         <v>1034</v>
       </c>
@@ -10980,7 +11001,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1">
       <c r="A53" s="5">
         <v>1036</v>
       </c>
@@ -11152,7 +11173,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" hidden="1">
       <c r="A54" s="5">
         <v>1037</v>
       </c>
@@ -11324,7 +11345,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" hidden="1">
       <c r="A55" s="5">
         <v>1040</v>
       </c>
@@ -11496,33 +11517,38 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:51">
+      <c r="A56" s="51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:51">
       <c r="D57" s="41"/>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:51">
       <c r="D59" s="42"/>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:51">
       <c r="D61" s="41"/>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:51">
       <c r="D63" s="42"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:4">
       <c r="D65" s="41"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:4">
       <c r="D66" s="42"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:4">
       <c r="D67" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
+    <filterColumn colId="47">
       <filters>
-        <filter val="908"/>
+        <filter val="Direct"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -11551,9 +11577,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="B2:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5">
       <c r="B2" t="s">
         <v>161</v>
       </c>
@@ -11567,7 +11593,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>164</v>
       </c>
@@ -11581,7 +11607,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>167</v>
       </c>
@@ -11594,7 +11620,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20166134-0068-44E4-897C-A3439A6356AD}">
   <dimension ref="D7:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -11602,7 +11628,7 @@
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="4:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:8" ht="30">
       <c r="D7" s="31" t="s">
         <v>6</v>
       </c>
@@ -11619,7 +11645,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:8" ht="15.75">
       <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
@@ -11636,7 +11662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:8" ht="15.75">
       <c r="D9" s="43" t="s">
         <v>98</v>
       </c>
@@ -11653,7 +11679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:8" ht="15.75">
       <c r="D10" s="43" t="s">
         <v>62</v>
       </c>
@@ -11670,7 +11696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:8" ht="15.75">
       <c r="D11" s="43" t="s">
         <v>68</v>
       </c>
@@ -11687,7 +11713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:8" ht="15.75">
       <c r="D12" s="23" t="s">
         <v>68</v>
       </c>
@@ -11704,7 +11730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:8" ht="15.75">
       <c r="D13" s="23" t="s">
         <v>68</v>
       </c>
@@ -11721,7 +11747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:8" ht="15.75">
       <c r="D14" s="43" t="s">
         <v>52</v>
       </c>
@@ -11738,7 +11764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:8" ht="15.75">
       <c r="D15" s="23" t="s">
         <v>57</v>
       </c>
@@ -11755,7 +11781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:8" ht="15.75">
       <c r="D16" s="43" t="s">
         <v>90</v>
       </c>
@@ -11772,7 +11798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:8" ht="15.75">
       <c r="D17" s="43" t="s">
         <v>96</v>
       </c>
@@ -11809,9 +11835,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D049-164C-47D4-96CD-56CBAA0ABF56}">
   <dimension ref="A1:BF3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" ht="45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -11978,7 +12004,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58">
       <c r="A2" s="5" t="s">
         <v>176</v>
       </c>
@@ -12138,7 +12164,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58">
       <c r="A3" s="5" t="s">
         <v>178</v>
       </c>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Porjects\HorseLuis\VTT Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Porjects\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364E7D07-101A-4478-91B4-7969C0CBC0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B0C978-180C-4956-B345-90E973C8D01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -1700,7 +1700,7 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2344,15 +2344,15 @@
         <v>74</v>
       </c>
       <c r="AI2" s="23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="23">
         <f t="shared" ref="AJ2:AJ33" si="6">+AI2+AH2</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM2" s="23">
         <f t="shared" ref="AM2:AM33" si="7">+AJ2+AL2</f>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Projects\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DFD585-0A89-4501-9298-04F2AE4E16D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E8B38-A866-4609-97C5-C3748C92A108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -758,7 +758,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294964316" uniqueCount="183">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -5608,7 +5608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF66"/>
@@ -5806,7 +5806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>138</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -6430,14 +6430,14 @@
         <v>60</v>
       </c>
       <c r="AL5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM5" s="3">
         <f>+AJ5+AL5</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AN5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO5" s="3">
         <f>+AM5+AN5</f>
@@ -6478,7 +6478,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>168</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>233</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>416</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>907</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>920</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>1039</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>1084</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>752</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>1006</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>1009</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>1010</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>1014</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>1015</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>1034</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1036</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1040</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>60</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>120</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>121</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>908</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>910</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>912</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>916</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>921</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>928</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>930</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>931</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>761</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>888</v>
       </c>
@@ -13357,7 +13357,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>1007</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>1037</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>904</v>
       </c>
@@ -13876,7 +13876,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>906</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>917</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>918</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>925</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>927</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>1005</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>1012</v>
       </c>
@@ -15086,7 +15086,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="49" t="s">
         <v>181</v>
       </c>
@@ -15112,6 +15112,11 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY56" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ROMANIA"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY56">
       <sortCondition ref="AI1:AI56"/>
     </sortState>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -758,7 +758,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294964316" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="183">
   <si>
     <t>Compte Consignee</t>
   </si>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Projects\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E8B38-A866-4609-97C5-C3748C92A108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8930C3-736F-46D2-9935-D44476D6102E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="155" r:id="rId6"/>
+    <pivotCache cacheId="194" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4820,7 +4820,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="194" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="51">
     <pivotField compact="0" outline="0" showAll="0">
@@ -5850,14 +5850,14 @@
         <v>1</v>
       </c>
       <c r="O2" s="3">
-        <f>IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
+        <f t="shared" ref="O2:O11" si="0">IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
         <v>8</v>
       </c>
       <c r="P2" s="3">
         <v>6</v>
       </c>
       <c r="Q2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
+        <f t="shared" ref="Q2:Q33" si="1">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
         <v>13</v>
       </c>
       <c r="R2" s="23">
@@ -5867,7 +5867,7 @@
         <v>12</v>
       </c>
       <c r="T2" s="23">
-        <f>+R2+S2-1</f>
+        <f t="shared" ref="T2:T9" si="2">+R2+S2-1</f>
         <v>20</v>
       </c>
       <c r="U2" s="23">
@@ -5878,7 +5878,7 @@
         <v>5</v>
       </c>
       <c r="W2" s="23">
-        <f>+U2+V2-1</f>
+        <f t="shared" ref="W2:W7" si="3">+U2+V2-1</f>
         <v>26</v>
       </c>
       <c r="X2" s="23">
@@ -5902,21 +5902,21 @@
         <v>41</v>
       </c>
       <c r="AF2" s="23">
-        <f>+AE2+AA2-1</f>
+        <f t="shared" ref="AF2:AF33" si="4">+AE2+AA2-1</f>
         <v>71</v>
       </c>
       <c r="AG2" s="23">
         <v>3</v>
       </c>
       <c r="AH2" s="23">
-        <f>+AF2+AG2</f>
+        <f t="shared" ref="AH2:AH33" si="5">+AF2+AG2</f>
         <v>74</v>
       </c>
       <c r="AI2" s="23">
         <v>0</v>
       </c>
       <c r="AJ2" s="23">
-        <f>+AI2+AH2</f>
+        <f t="shared" ref="AJ2:AJ33" si="6">+AI2+AH2</f>
         <v>74</v>
       </c>
       <c r="AK2" s="23"/>
@@ -5924,14 +5924,14 @@
         <v>5</v>
       </c>
       <c r="AM2" s="23">
-        <f>+AJ2+AL2</f>
+        <f t="shared" ref="AM2:AM33" si="7">+AJ2+AL2</f>
         <v>79</v>
       </c>
       <c r="AN2" s="23">
         <v>2</v>
       </c>
       <c r="AO2" s="23">
-        <f>+AM2+AN2</f>
+        <f t="shared" ref="AO2:AO33" si="8">+AM2+AN2</f>
         <v>81</v>
       </c>
       <c r="AP2" s="23">
@@ -5945,14 +5945,14 @@
         <v>91</v>
       </c>
       <c r="AS2" s="23">
-        <f>+AR2+7+AT2</f>
+        <f t="shared" ref="AS2:AS33" si="9">+AR2+7+AT2</f>
         <v>112</v>
       </c>
       <c r="AT2" s="23">
         <v>14</v>
       </c>
       <c r="AU2" s="3">
-        <f>+AA2-R2</f>
+        <f t="shared" ref="AU2:AU33" si="10">+AA2-R2</f>
         <v>22</v>
       </c>
       <c r="AV2" s="23" t="s">
@@ -6012,14 +6012,14 @@
         <v>1</v>
       </c>
       <c r="O3" s="3">
-        <f>IF(I3="SFK Freight Forwarder",M3,M3+N3-1)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="P3" s="3">
         <v>6</v>
       </c>
       <c r="Q3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",O3,O3+P3-1)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="R3" s="23">
@@ -6029,7 +6029,7 @@
         <v>12</v>
       </c>
       <c r="T3" s="23">
-        <f>+R3+S3-1</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="U3" s="23">
@@ -6040,7 +6040,7 @@
         <v>5</v>
       </c>
       <c r="W3" s="23">
-        <f>+U3+V3-1</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="X3" s="23">
@@ -6064,21 +6064,21 @@
         <v>34</v>
       </c>
       <c r="AF3" s="23">
-        <f>+AE3+AA3-1</f>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="AG3" s="23">
         <v>3</v>
       </c>
       <c r="AH3" s="23">
-        <f>+AF3+AG3</f>
+        <f t="shared" si="5"/>
         <v>72</v>
       </c>
       <c r="AI3" s="23">
         <v>0</v>
       </c>
       <c r="AJ3" s="23">
-        <f>+AI3+AH3</f>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="AK3" s="23"/>
@@ -6086,36 +6086,36 @@
         <v>2</v>
       </c>
       <c r="AM3" s="23">
-        <f>+AJ3+AL3</f>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="AN3" s="23">
         <v>1</v>
       </c>
       <c r="AO3" s="23">
-        <f>+AM3+AN3</f>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
       <c r="AP3" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" s="3">
-        <f>+AO3+AP3</f>
-        <v>78</v>
+        <f t="shared" ref="AQ3:AQ34" si="11">+AO3+AP3</f>
+        <v>77</v>
       </c>
       <c r="AR3" s="23">
-        <f>+AQ3+4</f>
-        <v>82</v>
+        <f>+AQ3+7</f>
+        <v>84</v>
       </c>
       <c r="AS3" s="23">
-        <f>+AR3+7+AT3</f>
-        <v>103</v>
+        <f t="shared" si="9"/>
+        <v>105</v>
       </c>
       <c r="AT3" s="23">
         <v>14</v>
       </c>
       <c r="AU3" s="3">
-        <f>+AA3-R3</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="AV3" s="23" t="s">
@@ -6169,44 +6169,44 @@
         <v>7</v>
       </c>
       <c r="M4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",L4,9)</f>
+        <f t="shared" ref="M4:M11" si="12">+IF(I4="SFK Freight Forwarder",L4,9)</f>
         <v>9</v>
       </c>
       <c r="N4" s="3">
         <v>14</v>
       </c>
       <c r="O4" s="3">
-        <f>IF(I4="SFK Freight Forwarder",M4,M4+N4-1)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="P4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P4:P9" si="13">+IF(I4="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",O4,O4+P4-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R4" s="3">
-        <f>9+N4</f>
+        <f t="shared" ref="R4:R9" si="14">9+N4</f>
         <v>23</v>
       </c>
       <c r="S4" s="3">
         <v>7</v>
       </c>
       <c r="T4" s="3">
-        <f>+R4+S4-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U4" s="3">
-        <f>+T4+1</f>
+        <f t="shared" ref="U4:U9" si="15">+T4+1</f>
         <v>30</v>
       </c>
       <c r="V4" s="3">
         <v>2</v>
       </c>
       <c r="W4" s="3">
-        <f>+U4+V4-1</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="X4" s="3">
@@ -6237,21 +6237,21 @@
         <v>52</v>
       </c>
       <c r="AF4" s="3">
-        <f>+AE4+AA4-1</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="AG4" s="6">
         <v>3</v>
       </c>
       <c r="AH4" s="6">
-        <f>+AF4+AG4</f>
+        <f t="shared" si="5"/>
         <v>88</v>
       </c>
       <c r="AI4" s="3">
         <v>0</v>
       </c>
       <c r="AJ4" s="3">
-        <f>+AI4+AH4</f>
+        <f t="shared" si="6"/>
         <v>88</v>
       </c>
       <c r="AK4" s="3" t="s">
@@ -6261,21 +6261,21 @@
         <v>2</v>
       </c>
       <c r="AM4" s="3">
-        <f>+AJ4+AL4</f>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="AN4" s="3">
         <v>2</v>
       </c>
       <c r="AO4" s="3">
-        <f>+AM4+AN4</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AP4" s="3">
         <v>6</v>
       </c>
       <c r="AQ4" s="3">
-        <f>+AO4+AP4</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR4" s="3">
@@ -6283,14 +6283,14 @@
         <v>105</v>
       </c>
       <c r="AS4" s="3">
-        <f>+AR4+7+AT4</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT4" s="3">
         <v>0</v>
       </c>
       <c r="AU4" s="3">
-        <f>+AA4-R4</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AV4" s="3" t="s">
@@ -6344,44 +6344,44 @@
         <v>7</v>
       </c>
       <c r="M5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",L5,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N5" s="3">
         <v>14</v>
       </c>
       <c r="O5" s="3">
-        <f>IF(I5="SFK Freight Forwarder",M5,M5+N5-1)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="P5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="Q5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",O5,O5+P5-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R5" s="3">
-        <f>9+N5</f>
+        <f t="shared" si="14"/>
         <v>23</v>
       </c>
       <c r="S5" s="3">
         <v>7</v>
       </c>
       <c r="T5" s="3">
-        <f>+R5+S5-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U5" s="3">
-        <f>+T5+1</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="V5" s="3">
         <v>2</v>
       </c>
       <c r="W5" s="3">
-        <f>+U5+V5-1</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="X5" s="3">
@@ -6409,21 +6409,21 @@
         <v>69</v>
       </c>
       <c r="AF5" s="3">
-        <f>+AE5+AA5-1</f>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="AG5" s="6">
         <v>3</v>
       </c>
       <c r="AH5" s="6">
-        <f>+AF5+AG5</f>
+        <f t="shared" si="5"/>
         <v>108</v>
       </c>
       <c r="AI5" s="3">
         <v>0</v>
       </c>
       <c r="AJ5" s="3">
-        <f>+AI5+AH5</f>
+        <f t="shared" si="6"/>
         <v>108</v>
       </c>
       <c r="AK5" s="3" t="s">
@@ -6433,36 +6433,36 @@
         <v>1</v>
       </c>
       <c r="AM5" s="3">
-        <f>+AJ5+AL5</f>
+        <f t="shared" si="7"/>
         <v>109</v>
       </c>
       <c r="AN5" s="3">
         <v>8</v>
       </c>
       <c r="AO5" s="3">
-        <f>+AM5+AN5</f>
+        <f t="shared" si="8"/>
         <v>117</v>
       </c>
       <c r="AP5" s="3">
         <v>2</v>
       </c>
       <c r="AQ5" s="3">
-        <f>+AO5+AP5</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR5" s="3">
-        <f>+AQ5+5</f>
-        <v>124</v>
+        <f>+AQ5+7</f>
+        <v>126</v>
       </c>
       <c r="AS5" s="3">
-        <f>+AR5+7+AT5</f>
-        <v>131</v>
+        <f t="shared" si="9"/>
+        <v>133</v>
       </c>
       <c r="AT5" s="3">
         <v>0</v>
       </c>
       <c r="AU5" s="3">
-        <f>+AA5-R5</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AV5" s="3" t="s">
@@ -6516,44 +6516,44 @@
         <v>7</v>
       </c>
       <c r="M6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",L6,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N6" s="3">
         <v>14</v>
       </c>
       <c r="O6" s="3">
-        <f>IF(I6="SFK Freight Forwarder",M6,M6+N6-1)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="P6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="Q6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",O6,O6+P6-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R6" s="3">
-        <f>9+N6</f>
+        <f t="shared" si="14"/>
         <v>23</v>
       </c>
       <c r="S6" s="3">
         <v>7</v>
       </c>
       <c r="T6" s="3">
-        <f>+R6+S6-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U6" s="3">
-        <f>+T6+1</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="V6" s="3">
         <v>2</v>
       </c>
       <c r="W6" s="3">
-        <f>+U6+V6-1</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="X6" s="3">
@@ -6566,7 +6566,7 @@
         <v>33</v>
       </c>
       <c r="AA6" s="6">
-        <f>+Z6+AB6-1</f>
+        <f t="shared" ref="AA6:AA11" si="16">+Z6+AB6-1</f>
         <v>38</v>
       </c>
       <c r="AB6" s="3">
@@ -6582,21 +6582,21 @@
         <v>45</v>
       </c>
       <c r="AF6" s="3">
-        <f>+AE6+AA6-1</f>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="AG6" s="6">
         <v>3</v>
       </c>
       <c r="AH6" s="6">
-        <f>+AF6+AG6</f>
+        <f t="shared" si="5"/>
         <v>85</v>
       </c>
       <c r="AI6" s="3">
         <v>0</v>
       </c>
       <c r="AJ6" s="3">
-        <f>+AI6+AH6</f>
+        <f t="shared" si="6"/>
         <v>85</v>
       </c>
       <c r="AK6" s="3" t="s">
@@ -6606,36 +6606,36 @@
         <v>2</v>
       </c>
       <c r="AM6" s="3">
-        <f>+AJ6+AL6</f>
+        <f t="shared" si="7"/>
         <v>87</v>
       </c>
       <c r="AN6" s="3">
         <v>1</v>
       </c>
       <c r="AO6" s="3">
-        <f>+AM6+AN6</f>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="AP6" s="3">
         <v>3</v>
       </c>
       <c r="AQ6" s="3">
-        <f>+AO6+AP6</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR6" s="3">
-        <f>+AQ6+7</f>
+        <f t="shared" ref="AR6:AR37" si="17">+AQ6+7</f>
         <v>98</v>
       </c>
       <c r="AS6" s="3">
-        <f>+AR6+7+AT6</f>
+        <f t="shared" si="9"/>
         <v>105</v>
       </c>
       <c r="AT6" s="3">
         <v>0</v>
       </c>
       <c r="AU6" s="3">
-        <f>+AA6-R6</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="AV6" s="3" t="s">
@@ -6689,44 +6689,44 @@
         <v>7</v>
       </c>
       <c r="M7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",L7,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N7" s="3">
         <v>14</v>
       </c>
       <c r="O7" s="3">
-        <f>IF(I7="SFK Freight Forwarder",M7,M7+N7-1)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="P7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="Q7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",O7,O7+P7-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R7" s="3">
-        <f>9+N7</f>
+        <f t="shared" si="14"/>
         <v>23</v>
       </c>
       <c r="S7" s="3">
         <v>7</v>
       </c>
       <c r="T7" s="3">
-        <f>+R7+S7-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U7" s="3">
-        <f>+T7+1</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="V7" s="3">
         <v>2</v>
       </c>
       <c r="W7" s="3">
-        <f>+U7+V7-1</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="X7" s="3">
@@ -6741,7 +6741,7 @@
         <v>31</v>
       </c>
       <c r="AA7" s="6">
-        <f>+Z7+AB7-1</f>
+        <f t="shared" si="16"/>
         <v>34</v>
       </c>
       <c r="AB7" s="3">
@@ -6757,21 +6757,21 @@
         <v>48</v>
       </c>
       <c r="AF7" s="3">
-        <f>+AE7+AA7-1</f>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AG7" s="6">
         <v>0</v>
       </c>
       <c r="AH7" s="6">
-        <f>+AF7+AG7</f>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="AI7" s="3">
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
-        <f>+AI7+AH7</f>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="AK7" s="3" t="s">
@@ -6781,36 +6781,36 @@
         <v>3</v>
       </c>
       <c r="AM7" s="3">
-        <f>+AJ7+AL7</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="AN7" s="3">
         <v>8</v>
       </c>
       <c r="AO7" s="3">
-        <f>+AM7+AN7</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AP7" s="3">
         <v>0</v>
       </c>
       <c r="AQ7" s="3">
-        <f>+AO7+AP7</f>
+        <f t="shared" si="11"/>
         <v>92</v>
       </c>
       <c r="AR7" s="3">
-        <f>+AQ7+7</f>
+        <f t="shared" si="17"/>
         <v>99</v>
       </c>
       <c r="AS7" s="3">
-        <f>+AR7+7+AT7</f>
+        <f t="shared" si="9"/>
         <v>106</v>
       </c>
       <c r="AT7" s="3">
         <v>0</v>
       </c>
       <c r="AU7" s="3">
-        <f>+AA7-R7</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AV7" s="3" t="s">
@@ -6864,37 +6864,37 @@
         <v>2</v>
       </c>
       <c r="M8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",L8,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N8" s="3">
         <v>14</v>
       </c>
       <c r="O8" s="3">
-        <f>IF(I8="SFK Freight Forwarder",M8,M8+N8-1)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="P8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="Q8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",O8,O8+P8-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R8" s="3">
-        <f>9+N8</f>
+        <f t="shared" si="14"/>
         <v>23</v>
       </c>
       <c r="S8" s="3">
         <v>7</v>
       </c>
       <c r="T8" s="3">
-        <f>+R8+S8-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U8" s="3">
-        <f>+T8+1</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="V8" s="3">
@@ -6913,7 +6913,7 @@
         <v>30</v>
       </c>
       <c r="AA8" s="48">
-        <f>+Z8+AB8-1</f>
+        <f t="shared" si="16"/>
         <v>32</v>
       </c>
       <c r="AB8" s="3">
@@ -6929,21 +6929,21 @@
         <v>55</v>
       </c>
       <c r="AF8" s="3">
-        <f>+AE8+AA8-1</f>
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
       <c r="AG8" s="6">
         <v>3</v>
       </c>
       <c r="AH8" s="6">
-        <f>+AF8+AG8</f>
+        <f t="shared" si="5"/>
         <v>89</v>
       </c>
       <c r="AI8" s="3">
         <v>0</v>
       </c>
       <c r="AJ8" s="3">
-        <f>+AI8+AH8</f>
+        <f t="shared" si="6"/>
         <v>89</v>
       </c>
       <c r="AK8" s="3" t="s">
@@ -6953,36 +6953,36 @@
         <v>4</v>
       </c>
       <c r="AM8" s="3">
-        <f>+AJ8+AL8</f>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="AN8" s="3">
         <v>2</v>
       </c>
       <c r="AO8" s="3">
-        <f>+AM8+AN8</f>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="AP8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ8" s="3">
-        <f>+AO8+AP8</f>
-        <v>96</v>
+        <f t="shared" si="11"/>
+        <v>98</v>
       </c>
       <c r="AR8" s="3">
-        <f>+AQ8+7</f>
-        <v>103</v>
+        <f t="shared" si="17"/>
+        <v>105</v>
       </c>
       <c r="AS8" s="3">
-        <f>+AR8+7+AT8</f>
-        <v>110</v>
+        <f t="shared" si="9"/>
+        <v>112</v>
       </c>
       <c r="AT8" s="3">
         <v>0</v>
       </c>
       <c r="AU8" s="3">
-        <f>+AA8-R8</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="AV8" s="3" t="s">
@@ -7036,37 +7036,37 @@
         <v>7</v>
       </c>
       <c r="M9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",L9,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N9" s="3">
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f>IF(I9="SFK Freight Forwarder",M9,M9+N9-1)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="P9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="Q9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",O9,O9+P9-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R9" s="3">
-        <f>9+N9</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="S9" s="3">
         <v>3</v>
       </c>
       <c r="T9" s="3">
-        <f>+R9+S9-1</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="U9" s="3">
-        <f>+T9+1</f>
+        <f t="shared" si="15"/>
         <v>19</v>
       </c>
       <c r="V9" s="3">
@@ -7087,7 +7087,7 @@
         <v>23</v>
       </c>
       <c r="AA9" s="6">
-        <f>+Z9+AB9-1</f>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="AB9" s="3">
@@ -7103,21 +7103,21 @@
         <v>40</v>
       </c>
       <c r="AF9" s="3">
-        <f>+AE9+AA9-1</f>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="AG9" s="6">
         <v>3</v>
       </c>
       <c r="AH9" s="6">
-        <f>+AF9+AG9</f>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="AI9" s="3">
         <v>0</v>
       </c>
       <c r="AJ9" s="3">
-        <f>+AI9+AH9</f>
+        <f t="shared" si="6"/>
         <v>67</v>
       </c>
       <c r="AK9" s="3">
@@ -7127,36 +7127,36 @@
         <v>13</v>
       </c>
       <c r="AM9" s="3">
-        <f>+AJ9+AL9</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AN9" s="3">
         <v>2</v>
       </c>
       <c r="AO9" s="3">
-        <f>+AM9+AN9</f>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="AP9" s="3">
         <v>0</v>
       </c>
       <c r="AQ9" s="3">
-        <f>+AO9+AP9</f>
+        <f t="shared" si="11"/>
         <v>82</v>
       </c>
       <c r="AR9" s="3">
-        <f>+AQ9+7</f>
+        <f t="shared" si="17"/>
         <v>89</v>
       </c>
       <c r="AS9" s="3">
-        <f>+AR9+7+AT9</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="AT9" s="3">
         <v>0</v>
       </c>
       <c r="AU9" s="3">
-        <f>+AA9-R9</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="AV9" s="3" t="s">
@@ -7210,21 +7210,21 @@
         <v>5</v>
       </c>
       <c r="M10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",L10,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N10" s="23">
         <v>2</v>
       </c>
       <c r="O10" s="3">
-        <f>IF(I10="SFK Freight Forwarder",M10,M10+N10-1)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="P10" s="3">
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",O10,O10+P10-1)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="R10" s="23">
@@ -7255,7 +7255,7 @@
         <v>22</v>
       </c>
       <c r="AA10" s="6">
-        <f>+Z10+AB10-1</f>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="AB10" s="23">
@@ -7267,21 +7267,21 @@
         <v>39</v>
       </c>
       <c r="AF10" s="23">
-        <f>+AE10+AA10-1</f>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="AG10" s="23">
         <v>3</v>
       </c>
       <c r="AH10" s="23">
-        <f>+AF10+AG10</f>
+        <f t="shared" si="5"/>
         <v>66</v>
       </c>
       <c r="AI10" s="23">
         <v>0</v>
       </c>
       <c r="AJ10" s="23">
-        <f>+AI10+AH10</f>
+        <f t="shared" si="6"/>
         <v>66</v>
       </c>
       <c r="AK10" s="23"/>
@@ -7289,36 +7289,36 @@
         <v>9</v>
       </c>
       <c r="AM10" s="23">
-        <f>+AJ10+AL10</f>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="AN10" s="23">
         <v>8</v>
       </c>
       <c r="AO10" s="23">
-        <f>+AM10+AN10</f>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="AP10" s="23">
         <v>2</v>
       </c>
       <c r="AQ10" s="23">
-        <f>+AO10+AP10</f>
+        <f t="shared" si="11"/>
         <v>85</v>
       </c>
       <c r="AR10" s="23">
-        <f>+AQ10+7</f>
+        <f t="shared" si="17"/>
         <v>92</v>
       </c>
       <c r="AS10" s="23">
-        <f>+AR10+7+AT10</f>
+        <f t="shared" si="9"/>
         <v>113</v>
       </c>
       <c r="AT10" s="23">
         <v>14</v>
       </c>
       <c r="AU10" s="3">
-        <f>+AA10-R10</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="AV10" s="23" t="s">
@@ -7372,21 +7372,21 @@
         <v>5</v>
       </c>
       <c r="M11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",L11,9)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="N11" s="23">
         <v>2</v>
       </c>
       <c r="O11" s="3">
-        <f>IF(I11="SFK Freight Forwarder",M11,M11+N11-1)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="P11" s="3">
         <v>5</v>
       </c>
       <c r="Q11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",O11,O11+P11-1)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="R11" s="23">
@@ -7405,7 +7405,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="23">
-        <f>+U11+V11-1</f>
+        <f t="shared" ref="W11:W55" si="18">+U11+V11-1</f>
         <v>18</v>
       </c>
       <c r="X11" s="23">
@@ -7418,7 +7418,7 @@
         <v>19</v>
       </c>
       <c r="AA11" s="6">
-        <f>+Z11+AB11-1</f>
+        <f t="shared" si="16"/>
         <v>22</v>
       </c>
       <c r="AB11" s="23">
@@ -7430,21 +7430,21 @@
         <v>46</v>
       </c>
       <c r="AF11" s="23">
-        <f>+AE11+AA11-1</f>
+        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="AG11" s="23">
         <v>3</v>
       </c>
       <c r="AH11" s="23">
-        <f>+AF11+AG11</f>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="AI11" s="23">
         <v>0</v>
       </c>
       <c r="AJ11" s="23">
-        <f>+AI11+AH11</f>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="AK11" s="23"/>
@@ -7452,36 +7452,36 @@
         <v>10</v>
       </c>
       <c r="AM11" s="23">
-        <f>+AJ11+AL11</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AN11" s="23">
         <v>2</v>
       </c>
       <c r="AO11" s="23">
-        <f>+AM11+AN11</f>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="AP11" s="23">
         <v>2</v>
       </c>
       <c r="AQ11" s="23">
-        <f>+AO11+AP11</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR11" s="23">
-        <f>+AQ11+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS11" s="23">
-        <f>+AR11+7+AT11</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT11" s="23">
         <v>14</v>
       </c>
       <c r="AU11" s="3">
-        <f>+AA11-R11</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="AV11" s="23" t="s">
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="Q12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",O12,O12+P12-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="R12" s="3">
@@ -7560,14 +7560,14 @@
         <v>21</v>
       </c>
       <c r="U12" s="3">
-        <f>+T12+1</f>
+        <f t="shared" ref="U12:U55" si="19">+T12+1</f>
         <v>22</v>
       </c>
       <c r="V12" s="3">
         <v>4</v>
       </c>
       <c r="W12" s="3">
-        <f>+U12+V12-1</f>
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
       <c r="X12" s="3">
@@ -7595,21 +7595,21 @@
         <v>50</v>
       </c>
       <c r="AF12" s="3">
-        <f>+AE12+AA12-1</f>
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="AG12" s="6">
         <v>3</v>
       </c>
       <c r="AH12" s="6">
-        <f>+AF12+AG12</f>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="AI12" s="3">
         <v>0</v>
       </c>
       <c r="AJ12" s="3">
-        <f>+AI12+AH12</f>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="AK12" s="3" t="s">
@@ -7619,36 +7619,36 @@
         <v>10</v>
       </c>
       <c r="AM12" s="3">
-        <f>+AJ12+AL12</f>
+        <f t="shared" si="7"/>
         <v>91</v>
       </c>
       <c r="AN12" s="3">
         <v>5</v>
       </c>
       <c r="AO12" s="3">
-        <f>+AM12+AN12</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="AP12" s="3">
         <v>3</v>
       </c>
       <c r="AQ12" s="3">
-        <f>+AO12+AP12</f>
+        <f t="shared" si="11"/>
         <v>99</v>
       </c>
       <c r="AR12" s="3">
-        <f>+AQ12+7</f>
+        <f t="shared" si="17"/>
         <v>106</v>
       </c>
       <c r="AS12" s="3">
-        <f>+AR12+7+AT12</f>
+        <f t="shared" si="9"/>
         <v>113</v>
       </c>
       <c r="AT12" s="3">
         <v>0</v>
       </c>
       <c r="AU12" s="3">
-        <f>+AA12-R12</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AV12" s="3" t="s">
@@ -7702,44 +7702,44 @@
         <v>7</v>
       </c>
       <c r="M13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",L13,9)</f>
+        <f t="shared" ref="M13:M22" si="20">+IF(I13="SFK Freight Forwarder",L13,9)</f>
         <v>9</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f>IF(I13="SFK Freight Forwarder",M13,M13+N13-1)</f>
+        <f t="shared" ref="O13:O22" si="21">IF(I13="SFK Freight Forwarder",M13,M13+N13-1)</f>
         <v>15</v>
       </c>
       <c r="P13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P13:P40" si="22">+IF(I13="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",O13,O13+P13-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R13" s="3">
-        <f>9+N13</f>
+        <f t="shared" ref="R13:R22" si="23">9+N13</f>
         <v>16</v>
       </c>
       <c r="S13" s="3">
         <v>7</v>
       </c>
       <c r="T13" s="3">
-        <f>+R13+S13-1</f>
+        <f t="shared" ref="T13:T55" si="24">+R13+S13-1</f>
         <v>22</v>
       </c>
       <c r="U13" s="3">
-        <f>+T13+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V13" s="3">
         <v>2</v>
       </c>
       <c r="W13" s="3">
-        <f>+U13+V13-1</f>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="X13" s="3">
@@ -7768,21 +7768,21 @@
         <v>41</v>
       </c>
       <c r="AF13" s="3">
-        <f>+AE13+AA13-1</f>
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="AG13" s="6">
         <v>3</v>
       </c>
       <c r="AH13" s="6">
-        <f>+AF13+AG13</f>
+        <f t="shared" si="5"/>
         <v>76</v>
       </c>
       <c r="AI13" s="3">
         <v>0</v>
       </c>
       <c r="AJ13" s="3">
-        <f>+AI13+AH13</f>
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -7792,36 +7792,36 @@
         <v>2</v>
       </c>
       <c r="AM13" s="3">
-        <f>+AJ13+AL13</f>
+        <f t="shared" si="7"/>
         <v>78</v>
       </c>
       <c r="AN13" s="3">
         <v>2</v>
       </c>
       <c r="AO13" s="3">
-        <f>+AM13+AN13</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="AP13" s="3">
         <v>4</v>
       </c>
       <c r="AQ13" s="3">
-        <f>+AO13+AP13</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR13" s="3">
-        <f>+AQ13+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS13" s="3">
-        <f>+AR13+7+AT13</f>
+        <f t="shared" si="9"/>
         <v>104</v>
       </c>
       <c r="AT13" s="3">
         <v>6</v>
       </c>
       <c r="AU13" s="3">
-        <f>+AA13-R13</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="AV13" s="3" t="s">
@@ -7875,44 +7875,44 @@
         <v>7</v>
       </c>
       <c r="M14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",L14,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N14" s="3">
         <v>7</v>
       </c>
       <c r="O14" s="3">
-        <f>IF(I14="SFK Freight Forwarder",M14,M14+N14-1)</f>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="P14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",O14,O14+P14-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R14" s="3">
-        <f>9+N14</f>
+        <f t="shared" si="23"/>
         <v>16</v>
       </c>
       <c r="S14" s="3">
         <v>7</v>
       </c>
       <c r="T14" s="3">
-        <f>+R14+S14-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U14" s="3">
-        <f>+T14+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V14" s="3">
         <v>4</v>
       </c>
       <c r="W14" s="3">
-        <f>+U14+V14-1</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="X14" s="3">
@@ -7941,21 +7941,21 @@
         <v>46</v>
       </c>
       <c r="AF14" s="3">
-        <f>+AE14+AA14-1</f>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="AG14" s="6">
         <v>3</v>
       </c>
       <c r="AH14" s="6">
-        <f>+AF14+AG14</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
-        <f>+AI14+AH14</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AK14" s="3" t="s">
@@ -7965,36 +7965,36 @@
         <v>4</v>
       </c>
       <c r="AM14" s="3">
-        <f>+AJ14+AL14</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="AN14" s="3">
         <v>3</v>
       </c>
       <c r="AO14" s="3">
-        <f>+AM14+AN14</f>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="AP14" s="3">
         <v>4</v>
       </c>
       <c r="AQ14" s="3">
-        <f>+AO14+AP14</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR14" s="3">
-        <f>+AQ14+7</f>
+        <f t="shared" si="17"/>
         <v>98</v>
       </c>
       <c r="AS14" s="3">
-        <f>+AR14+7+AT14</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT14" s="3">
         <v>7</v>
       </c>
       <c r="AU14" s="3">
-        <f>+AA14-R14</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="AV14" s="3" t="s">
@@ -8010,7 +8010,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>901</v>
       </c>
@@ -8048,44 +8048,44 @@
         <v>7</v>
       </c>
       <c r="M15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",L15,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N15" s="3">
         <v>7</v>
       </c>
       <c r="O15" s="3">
-        <f>IF(I15="SFK Freight Forwarder",M15,M15+N15-1)</f>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="P15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",O15,O15+P15-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R15" s="3">
-        <f>9+N15</f>
+        <f t="shared" si="23"/>
         <v>16</v>
       </c>
       <c r="S15" s="3">
         <v>7</v>
       </c>
       <c r="T15" s="3">
-        <f>+R15+S15-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U15" s="3">
-        <f>+T15+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V15" s="3">
         <v>4</v>
       </c>
       <c r="W15" s="3">
-        <f>+U15+V15-1</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="X15" s="3">
@@ -8114,21 +8114,21 @@
         <v>49</v>
       </c>
       <c r="AF15" s="3">
-        <f>+AE15+AA15-1</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="AG15" s="6">
         <v>3</v>
       </c>
       <c r="AH15" s="6">
-        <f>+AF15+AG15</f>
+        <f t="shared" si="5"/>
         <v>83</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
       </c>
       <c r="AJ15" s="3">
-        <f>+AI15+AH15</f>
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
       <c r="AK15" s="3" t="s">
@@ -8138,36 +8138,36 @@
         <v>1</v>
       </c>
       <c r="AM15" s="3">
-        <f>+AJ15+AL15</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="AN15" s="3">
         <v>8</v>
       </c>
       <c r="AO15" s="3">
-        <f>+AM15+AN15</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AP15" s="3">
         <v>6</v>
       </c>
       <c r="AQ15" s="3">
-        <f>+AO15+AP15</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR15" s="3">
-        <f>+AQ15+7</f>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="AS15" s="3">
-        <f>+AR15+7+AT15</f>
+        <f t="shared" si="9"/>
         <v>119</v>
       </c>
       <c r="AT15" s="3">
         <v>7</v>
       </c>
       <c r="AU15" s="3">
-        <f>+AA15-R15</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="AV15" s="3" t="s">
@@ -8221,44 +8221,44 @@
         <v>7</v>
       </c>
       <c r="M16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",L16,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N16" s="3">
         <v>7</v>
       </c>
       <c r="O16" s="3">
-        <f>IF(I16="SFK Freight Forwarder",M16,M16+N16-1)</f>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="P16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",O16,O16+P16-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R16" s="3">
-        <f>9+N16</f>
+        <f t="shared" si="23"/>
         <v>16</v>
       </c>
       <c r="S16" s="3">
         <v>7</v>
       </c>
       <c r="T16" s="3">
-        <f>+R16+S16-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U16" s="3">
-        <f>+T16+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V16" s="3">
         <v>1</v>
       </c>
       <c r="W16" s="3">
-        <f>+U16+V16-1</f>
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
       <c r="X16" s="3">
@@ -8287,21 +8287,21 @@
         <v>40</v>
       </c>
       <c r="AF16" s="3">
-        <f>+AE16+AA16-1</f>
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="AG16" s="6">
         <v>3</v>
       </c>
       <c r="AH16" s="6">
-        <f>+AF16+AG16</f>
+        <f t="shared" si="5"/>
         <v>76</v>
       </c>
       <c r="AI16" s="3">
         <v>0</v>
       </c>
       <c r="AJ16" s="3">
-        <f>+AI16+AH16</f>
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="AK16" s="3" t="s">
@@ -8311,36 +8311,36 @@
         <v>2</v>
       </c>
       <c r="AM16" s="3">
-        <f>+AJ16+AL16</f>
+        <f t="shared" si="7"/>
         <v>78</v>
       </c>
       <c r="AN16" s="3">
         <v>2</v>
       </c>
       <c r="AO16" s="3">
-        <f>+AM16+AN16</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="AP16" s="3">
         <v>4</v>
       </c>
       <c r="AQ16" s="3">
-        <f>+AO16+AP16</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR16" s="3">
-        <f>+AQ16+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS16" s="3">
-        <f>+AR16+7+AT16</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT16" s="3">
         <v>14</v>
       </c>
       <c r="AU16" s="3">
-        <f>+AA16-R16</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="AV16" s="3" t="s">
@@ -8356,7 +8356,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -8394,44 +8394,44 @@
         <v>7</v>
       </c>
       <c r="M17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",L17,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N17" s="3">
         <v>14</v>
       </c>
       <c r="O17" s="3">
-        <f>IF(I17="SFK Freight Forwarder",M17,M17+N17-1)</f>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="P17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",O17,O17+P17-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R17" s="3">
-        <f>9+N17</f>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="S17" s="3">
         <v>7</v>
       </c>
       <c r="T17" s="3">
-        <f>+R17+S17-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U17" s="3">
-        <f>+T17+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V17" s="3">
         <v>2</v>
       </c>
       <c r="W17" s="3">
-        <f>+U17+V17-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X17" s="3">
@@ -8459,21 +8459,21 @@
         <v>43</v>
       </c>
       <c r="AF17" s="3">
-        <f>+AE17+AA17-1</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="AG17" s="6">
         <v>3</v>
       </c>
       <c r="AH17" s="6">
-        <f>+AF17+AG17</f>
+        <f t="shared" si="5"/>
         <v>83</v>
       </c>
       <c r="AI17" s="3">
         <v>0</v>
       </c>
       <c r="AJ17" s="3">
-        <f>+AI17+AH17</f>
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
       <c r="AK17" s="3" t="s">
@@ -8483,36 +8483,36 @@
         <v>15</v>
       </c>
       <c r="AM17" s="3">
-        <f>+AJ17+AL17</f>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
       <c r="AN17" s="3">
         <v>8</v>
       </c>
       <c r="AO17" s="3">
-        <f>+AM17+AN17</f>
+        <f t="shared" si="8"/>
         <v>106</v>
       </c>
       <c r="AP17" s="3">
         <v>6</v>
       </c>
       <c r="AQ17" s="3">
-        <f>+AO17+AP17</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AR17" s="3">
-        <f>+AQ17+7</f>
+        <f t="shared" si="17"/>
         <v>119</v>
       </c>
       <c r="AS17" s="3">
-        <f>+AR17+7+AT17</f>
+        <f t="shared" si="9"/>
         <v>139</v>
       </c>
       <c r="AT17" s="3">
         <v>13</v>
       </c>
       <c r="AU17" s="3">
-        <f>+AA17-R17</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="AV17" s="3" t="s">
@@ -8566,44 +8566,44 @@
         <v>7</v>
       </c>
       <c r="M18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",L18,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N18" s="3">
         <v>14</v>
       </c>
       <c r="O18" s="3">
-        <f>IF(I18="SFK Freight Forwarder",M18,M18+N18-1)</f>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="P18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",O18,O18+P18-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R18" s="3">
-        <f>9+N18</f>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="S18" s="3">
         <v>7</v>
       </c>
       <c r="T18" s="3">
-        <f>+R18+S18-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U18" s="3">
-        <f>+T18+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V18" s="3">
         <v>3</v>
       </c>
       <c r="W18" s="3">
-        <f>+U18+V18-1</f>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="X18" s="3">
@@ -8616,7 +8616,7 @@
         <v>37</v>
       </c>
       <c r="AA18" s="6">
-        <f>+Z18+AB18-1</f>
+        <f t="shared" ref="AA18:AA34" si="25">+Z18+AB18-1</f>
         <v>39</v>
       </c>
       <c r="AB18" s="3">
@@ -8632,21 +8632,21 @@
         <v>39</v>
       </c>
       <c r="AF18" s="3">
-        <f>+AE18+AA18-1</f>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="AG18" s="6">
         <v>3</v>
       </c>
       <c r="AH18" s="6">
-        <f>+AF18+AG18</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="AI18" s="3">
         <v>0</v>
       </c>
       <c r="AJ18" s="3">
-        <f>+AI18+AH18</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AK18" s="3" t="s">
@@ -8656,36 +8656,36 @@
         <v>3</v>
       </c>
       <c r="AM18" s="3">
-        <f>+AJ18+AL18</f>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="AN18" s="3">
         <v>9</v>
       </c>
       <c r="AO18" s="3">
-        <f>+AM18+AN18</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AP18" s="3">
         <v>6</v>
       </c>
       <c r="AQ18" s="3">
-        <f>+AO18+AP18</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR18" s="3">
-        <f>+AQ18+7</f>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="AS18" s="3">
-        <f>+AR18+7+AT18</f>
+        <f t="shared" si="9"/>
         <v>126</v>
       </c>
       <c r="AT18" s="3">
         <v>14</v>
       </c>
       <c r="AU18" s="3">
-        <f>+AA18-R18</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="AV18" s="3" t="s">
@@ -8701,7 +8701,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>924</v>
       </c>
@@ -8739,44 +8739,44 @@
         <v>7</v>
       </c>
       <c r="M19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",L19,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N19" s="3">
         <v>7</v>
       </c>
       <c r="O19" s="3">
-        <f>IF(I19="SFK Freight Forwarder",M19,M19+N19-1)</f>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="P19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",O19,O19+P19-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R19" s="3">
-        <f>9+N19</f>
+        <f t="shared" si="23"/>
         <v>16</v>
       </c>
       <c r="S19" s="3">
         <v>7</v>
       </c>
       <c r="T19" s="3">
-        <f>+R19+S19-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U19" s="3">
-        <f>+T19+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V19" s="3">
         <v>3</v>
       </c>
       <c r="W19" s="3">
-        <f>+U19+V19-1</f>
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
       <c r="X19" s="3">
@@ -8789,7 +8789,7 @@
         <v>30</v>
       </c>
       <c r="AA19" s="6">
-        <f>+Z19+AB19-1</f>
+        <f t="shared" si="25"/>
         <v>32</v>
       </c>
       <c r="AB19" s="3">
@@ -8805,21 +8805,21 @@
         <v>17</v>
       </c>
       <c r="AF19" s="3">
-        <f>+AE19+AA19-1</f>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="AG19" s="6">
         <v>3</v>
       </c>
       <c r="AH19" s="6">
-        <f>+AF19+AG19</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="AI19" s="3">
         <v>0</v>
       </c>
       <c r="AJ19" s="3">
-        <f>+AI19+AH19</f>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
       <c r="AK19" s="3" t="s">
@@ -8829,36 +8829,36 @@
         <v>8</v>
       </c>
       <c r="AM19" s="3">
-        <f>+AJ19+AL19</f>
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="AN19" s="3">
         <v>8</v>
       </c>
       <c r="AO19" s="3">
-        <f>+AM19+AN19</f>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
       <c r="AP19" s="3">
         <v>3</v>
       </c>
       <c r="AQ19" s="3">
-        <f>+AO19+AP19</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="AR19" s="3">
-        <f>+AQ19+7</f>
+        <f t="shared" si="17"/>
         <v>77</v>
       </c>
       <c r="AS19" s="3">
-        <f>+AR19+7+AT19</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AT19" s="3">
         <v>0</v>
       </c>
       <c r="AU19" s="3">
-        <f>+AA19-R19</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="AV19" s="3" t="s">
@@ -8874,7 +8874,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>932</v>
       </c>
@@ -8912,44 +8912,44 @@
         <v>7</v>
       </c>
       <c r="M20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",L20,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N20" s="3">
         <v>14</v>
       </c>
       <c r="O20" s="3">
-        <f>IF(I20="SFK Freight Forwarder",M20,M20+N20-1)</f>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="P20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",O20,O20+P20-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R20" s="3">
-        <f>9+N20</f>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="S20" s="3">
         <v>7</v>
       </c>
       <c r="T20" s="3">
-        <f>+R20+S20-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U20" s="3">
-        <f>+T20+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V20" s="3">
         <v>1</v>
       </c>
       <c r="W20" s="3">
-        <f>+U20+V20-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X20" s="3">
@@ -8962,7 +8962,7 @@
         <v>35</v>
       </c>
       <c r="AA20" s="6">
-        <f>+Z20+AB20-1</f>
+        <f t="shared" si="25"/>
         <v>37</v>
       </c>
       <c r="AB20" s="3">
@@ -8978,21 +8978,21 @@
         <v>58</v>
       </c>
       <c r="AF20" s="3">
-        <f>+AE20+AA20-1</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="AG20" s="6">
         <v>3</v>
       </c>
       <c r="AH20" s="6">
-        <f>+AF20+AG20</f>
+        <f t="shared" si="5"/>
         <v>97</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <f>+AI20+AH20</f>
+        <f t="shared" si="6"/>
         <v>97</v>
       </c>
       <c r="AK20" s="3" t="s">
@@ -9002,36 +9002,36 @@
         <v>8</v>
       </c>
       <c r="AM20" s="3">
-        <f>+AJ20+AL20</f>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="AN20" s="3">
         <v>8</v>
       </c>
       <c r="AO20" s="3">
-        <f>+AM20+AN20</f>
+        <f t="shared" si="8"/>
         <v>113</v>
       </c>
       <c r="AP20" s="3">
         <v>6</v>
       </c>
       <c r="AQ20" s="3">
-        <f>+AO20+AP20</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR20" s="3">
-        <f>+AQ20+7</f>
+        <f t="shared" si="17"/>
         <v>126</v>
       </c>
       <c r="AS20" s="3">
-        <f>+AR20+7+AT20</f>
+        <f t="shared" si="9"/>
         <v>147</v>
       </c>
       <c r="AT20" s="3">
         <v>14</v>
       </c>
       <c r="AU20" s="3">
-        <f>+AA20-R20</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AV20" s="3" t="s">
@@ -9085,44 +9085,44 @@
         <v>7</v>
       </c>
       <c r="M21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",L21,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N21" s="3">
         <v>21</v>
       </c>
       <c r="O21" s="3">
-        <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="P21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="R21" s="3">
-        <f>9+N21</f>
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
-        <f>+R21+S21-1</f>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="U21" s="3">
-        <f>+T21+1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="V21" s="3">
         <v>1</v>
       </c>
       <c r="W21" s="3">
-        <f>+U21+V21-1</f>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="X21" s="3">
@@ -9135,7 +9135,7 @@
         <v>42</v>
       </c>
       <c r="AA21" s="6">
-        <f>+Z21+AB21-1</f>
+        <f t="shared" si="25"/>
         <v>44</v>
       </c>
       <c r="AB21" s="3">
@@ -9151,21 +9151,21 @@
         <v>40</v>
       </c>
       <c r="AF21" s="3">
-        <f>+AE21+AA21-1</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
-        <f>+AF21+AG21</f>
+        <f t="shared" si="5"/>
         <v>86</v>
       </c>
       <c r="AI21" s="3">
         <v>0</v>
       </c>
       <c r="AJ21" s="3">
-        <f>+AI21+AH21</f>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="AK21" s="3" t="s">
@@ -9175,36 +9175,36 @@
         <v>2</v>
       </c>
       <c r="AM21" s="3">
-        <f>+AJ21+AL21</f>
+        <f t="shared" si="7"/>
         <v>88</v>
       </c>
       <c r="AN21" s="3">
         <v>3</v>
       </c>
       <c r="AO21" s="3">
-        <f>+AM21+AN21</f>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="AP21" s="3">
         <v>0</v>
       </c>
       <c r="AQ21" s="3">
-        <f>+AO21+AP21</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR21" s="3">
-        <f>+AQ21+7</f>
+        <f t="shared" si="17"/>
         <v>98</v>
       </c>
       <c r="AS21" s="3">
-        <f>+AR21+7+AT21</f>
+        <f t="shared" si="9"/>
         <v>105</v>
       </c>
       <c r="AT21" s="3">
         <v>0</v>
       </c>
       <c r="AU21" s="3">
-        <f>+AA21-R21</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AV21" s="3" t="s">
@@ -9258,44 +9258,44 @@
         <v>7</v>
       </c>
       <c r="M22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",L22,9)</f>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="N22" s="3">
         <v>14</v>
       </c>
       <c r="O22" s="3">
-        <f>IF(I22="SFK Freight Forwarder",M22,M22+N22-1)</f>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="P22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",O22,O22+P22-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R22" s="3">
-        <f>9+N22</f>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="S22" s="3">
         <v>7</v>
       </c>
       <c r="T22" s="3">
-        <f>+R22+S22-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U22" s="3">
-        <f>+T22+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V22" s="3">
         <v>2</v>
       </c>
       <c r="W22" s="3">
-        <f>+U22+V22-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X22" s="3">
@@ -9308,7 +9308,7 @@
         <v>39</v>
       </c>
       <c r="AA22" s="6">
-        <f>+Z22+AB22-1</f>
+        <f t="shared" si="25"/>
         <v>41</v>
       </c>
       <c r="AB22" s="3">
@@ -9324,21 +9324,21 @@
         <v>35</v>
       </c>
       <c r="AF22" s="3">
-        <f>+AE22+AA22-1</f>
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="AG22" s="6">
         <v>3</v>
       </c>
       <c r="AH22" s="6">
-        <f>+AF22+AG22</f>
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
       <c r="AJ22" s="3">
-        <f>+AI22+AH22</f>
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
       <c r="AK22" s="3" t="s">
@@ -9348,36 +9348,36 @@
         <v>2</v>
       </c>
       <c r="AM22" s="3">
-        <f>+AJ22+AL22</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AN22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3">
-        <f>+AM22+AN22</f>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="AP22" s="3">
         <v>2</v>
       </c>
       <c r="AQ22" s="3">
-        <f>+AO22+AP22</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR22" s="3">
-        <f>+AQ22+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS22" s="3">
-        <f>+AR22+7+AT22</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AT22" s="3">
         <v>0</v>
       </c>
       <c r="AU22" s="3">
-        <f>+AA22-R22</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="AV22" s="3" t="s">
@@ -9440,11 +9440,11 @@
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",O23,O23+P23-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R23" s="3">
@@ -9454,18 +9454,18 @@
         <v>7</v>
       </c>
       <c r="T23" s="3">
-        <f>+R23+S23-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U23" s="3">
-        <f>+T23+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V23" s="3">
         <v>8</v>
       </c>
       <c r="W23" s="3">
-        <f>+U23+V23-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X23" s="3">
@@ -9479,7 +9479,7 @@
         <v>33</v>
       </c>
       <c r="AA23" s="6">
-        <f>+Z23+AB23-1</f>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="AB23" s="3">
@@ -9495,21 +9495,21 @@
         <v>43</v>
       </c>
       <c r="AF23" s="3">
-        <f>+AE23+AA23-1</f>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="AG23" s="6">
         <v>3</v>
       </c>
       <c r="AH23" s="6">
-        <f>+AF23+AG23</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="AI23" s="3">
         <v>0</v>
       </c>
       <c r="AJ23" s="3">
-        <f>+AI23+AH23</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AK23" s="3" t="s">
@@ -9519,36 +9519,36 @@
         <v>2</v>
       </c>
       <c r="AM23" s="3">
-        <f>+AJ23+AL23</f>
+        <f t="shared" si="7"/>
         <v>82</v>
       </c>
       <c r="AN23" s="3">
         <v>2</v>
       </c>
       <c r="AO23" s="3">
-        <f>+AM23+AN23</f>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="AP23" s="3">
         <v>0</v>
       </c>
       <c r="AQ23" s="3">
-        <f>+AO23+AP23</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR23" s="3">
-        <f>+AQ23+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS23" s="3">
-        <f>+AR23+7+AT23</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AT23" s="3">
         <v>0</v>
       </c>
       <c r="AU23" s="3">
-        <f>+AA23-R23</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="AV23" s="3" t="s">
@@ -9608,37 +9608,37 @@
         <v>14</v>
       </c>
       <c r="O24" s="3">
-        <f>IF(I24="SFK Freight Forwarder",M24,M24+N24-1)</f>
+        <f t="shared" ref="O24:O55" si="26">IF(I24="SFK Freight Forwarder",M24,M24+N24-1)</f>
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",O24,O24+P24-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <f>9+N24</f>
+        <f t="shared" ref="R24:R43" si="27">9+N24</f>
         <v>23</v>
       </c>
       <c r="S24" s="3">
         <v>7</v>
       </c>
       <c r="T24" s="3">
-        <f>+R24+S24-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U24" s="3">
-        <f>+T24+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V24" s="3">
         <v>1</v>
       </c>
       <c r="W24" s="3">
-        <f>+U24+V24-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X24" s="3">
@@ -9651,7 +9651,7 @@
         <v>31</v>
       </c>
       <c r="AA24" s="6">
-        <f>+Z24+AB24-1</f>
+        <f t="shared" si="25"/>
         <v>34</v>
       </c>
       <c r="AB24" s="3">
@@ -9667,21 +9667,21 @@
         <v>58</v>
       </c>
       <c r="AF24" s="3">
-        <f>+AE24+AA24-1</f>
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="AG24" s="6">
         <v>3</v>
       </c>
       <c r="AH24" s="6">
-        <f>+AF24+AG24</f>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
       <c r="AJ24" s="3">
-        <f>+AI24+AH24</f>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="AK24" s="3" t="s">
@@ -9691,36 +9691,36 @@
         <v>1</v>
       </c>
       <c r="AM24" s="3">
-        <f>+AJ24+AL24</f>
+        <f t="shared" si="7"/>
         <v>95</v>
       </c>
       <c r="AN24" s="3">
         <v>4</v>
       </c>
       <c r="AO24" s="3">
-        <f>+AM24+AN24</f>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="AP24" s="3">
         <v>6</v>
       </c>
       <c r="AQ24" s="3">
-        <f>+AO24+AP24</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR24" s="3">
-        <f>+AQ24+7</f>
+        <f t="shared" si="17"/>
         <v>112</v>
       </c>
       <c r="AS24" s="3">
-        <f>+AR24+7+AT24</f>
+        <f t="shared" si="9"/>
         <v>119</v>
       </c>
       <c r="AT24" s="3">
         <v>0</v>
       </c>
       <c r="AU24" s="3">
-        <f>+AA24-R24</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AV24" s="3" t="s">
@@ -9780,37 +9780,37 @@
         <v>14</v>
       </c>
       <c r="O25" s="3">
-        <f>IF(I25="SFK Freight Forwarder",M25,M25+N25-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",O25,O25+P25-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R25" s="3">
-        <f>9+N25</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S25" s="3">
         <v>7</v>
       </c>
       <c r="T25" s="3">
-        <f>+R25+S25-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U25" s="3">
-        <f>+T25+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V25" s="3">
         <v>1</v>
       </c>
       <c r="W25" s="3">
-        <f>+U25+V25-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X25" s="3">
@@ -9823,7 +9823,7 @@
         <v>36</v>
       </c>
       <c r="AA25" s="6">
-        <f>+Z25+AB25-1</f>
+        <f t="shared" si="25"/>
         <v>37</v>
       </c>
       <c r="AB25" s="3">
@@ -9839,21 +9839,21 @@
         <v>53</v>
       </c>
       <c r="AF25" s="3">
-        <f>+AE25+AA25-1</f>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="AG25" s="6">
         <v>3</v>
       </c>
       <c r="AH25" s="6">
-        <f>+AF25+AG25</f>
+        <f t="shared" si="5"/>
         <v>92</v>
       </c>
       <c r="AI25" s="3">
         <v>0</v>
       </c>
       <c r="AJ25" s="3">
-        <f>+AI25+AH25</f>
+        <f t="shared" si="6"/>
         <v>92</v>
       </c>
       <c r="AK25" s="3" t="s">
@@ -9863,36 +9863,36 @@
         <v>2</v>
       </c>
       <c r="AM25" s="3">
-        <f>+AJ25+AL25</f>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="AN25" s="3">
         <v>2</v>
       </c>
       <c r="AO25" s="3">
-        <f>+AM25+AN25</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="AP25" s="3">
         <v>2</v>
       </c>
       <c r="AQ25" s="3">
-        <f>+AO25+AP25</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR25" s="3">
-        <f>+AQ25+7</f>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="AS25" s="3">
-        <f>+AR25+7+AT25</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT25" s="3">
         <v>0</v>
       </c>
       <c r="AU25" s="3">
-        <f>+AA25-R25</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AV25" s="3" t="s">
@@ -9952,37 +9952,37 @@
         <v>14</v>
       </c>
       <c r="O26" s="3">
-        <f>IF(I26="SFK Freight Forwarder",M26,M26+N26-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",O26,O26+P26-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <f>9+N26</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S26" s="3">
         <v>7</v>
       </c>
       <c r="T26" s="3">
-        <f>+R26+S26-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U26" s="3">
-        <f>+T26+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V26" s="3">
         <v>1</v>
       </c>
       <c r="W26" s="3">
-        <f>+U26+V26-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X26" s="3">
@@ -9995,7 +9995,7 @@
         <v>33</v>
       </c>
       <c r="AA26" s="6">
-        <f>+Z26+AB26-1</f>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
       <c r="AB26" s="3">
@@ -10011,21 +10011,21 @@
         <v>63</v>
       </c>
       <c r="AF26" s="3">
-        <f>+AE26+AA26-1</f>
+        <f t="shared" si="4"/>
         <v>98</v>
       </c>
       <c r="AG26" s="6">
         <v>3</v>
       </c>
       <c r="AH26" s="6">
-        <f>+AF26+AG26</f>
+        <f t="shared" si="5"/>
         <v>101</v>
       </c>
       <c r="AI26" s="3">
         <v>0</v>
       </c>
       <c r="AJ26" s="3">
-        <f>+AI26+AH26</f>
+        <f t="shared" si="6"/>
         <v>101</v>
       </c>
       <c r="AK26" s="3" t="s">
@@ -10035,36 +10035,36 @@
         <v>4</v>
       </c>
       <c r="AM26" s="3">
-        <f>+AJ26+AL26</f>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="AN26" s="3">
         <v>3</v>
       </c>
       <c r="AO26" s="3">
-        <f>+AM26+AN26</f>
+        <f t="shared" si="8"/>
         <v>108</v>
       </c>
       <c r="AP26" s="3">
         <v>4</v>
       </c>
       <c r="AQ26" s="3">
-        <f>+AO26+AP26</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AR26" s="3">
-        <f>+AQ26+7</f>
+        <f t="shared" si="17"/>
         <v>119</v>
       </c>
       <c r="AS26" s="3">
-        <f>+AR26+7+AT26</f>
+        <f t="shared" si="9"/>
         <v>126</v>
       </c>
       <c r="AT26" s="3">
         <v>0</v>
       </c>
       <c r="AU26" s="3">
-        <f>+AA26-R26</f>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="AV26" s="3" t="s">
@@ -10124,37 +10124,37 @@
         <v>14</v>
       </c>
       <c r="O27" s="3">
-        <f>IF(I27="SFK Freight Forwarder",M27,M27+N27-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",O27,O27+P27-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <f>9+N27</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S27" s="3">
         <v>7</v>
       </c>
       <c r="T27" s="3">
-        <f>+R27+S27-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U27" s="3">
-        <f>+T27+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V27" s="3">
         <v>2</v>
       </c>
       <c r="W27" s="3">
-        <f>+U27+V27-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X27" s="3">
@@ -10167,7 +10167,7 @@
         <v>39</v>
       </c>
       <c r="AA27" s="6">
-        <f>+Z27+AB27-1</f>
+        <f t="shared" si="25"/>
         <v>44</v>
       </c>
       <c r="AB27" s="3">
@@ -10183,21 +10183,21 @@
         <v>17</v>
       </c>
       <c r="AF27" s="3">
-        <f>+AE27+AA27-1</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
-        <f>+AF27+AG27</f>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AI27" s="3">
         <v>0</v>
       </c>
       <c r="AJ27" s="3">
-        <f>+AI27+AH27</f>
+        <f t="shared" si="6"/>
         <v>63</v>
       </c>
       <c r="AK27" s="3" t="s">
@@ -10207,36 +10207,36 @@
         <v>0</v>
       </c>
       <c r="AM27" s="3">
-        <f>+AJ27+AL27</f>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AN27" s="3">
         <v>0</v>
       </c>
       <c r="AO27" s="3">
-        <f>+AM27+AN27</f>
+        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="AP27" s="3">
         <v>0</v>
       </c>
       <c r="AQ27" s="3">
-        <f>+AO27+AP27</f>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="AR27" s="3">
-        <f>+AQ27+7</f>
+        <f t="shared" si="17"/>
         <v>70</v>
       </c>
       <c r="AS27" s="3">
-        <f>+AR27+7+AT27</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AT27" s="3">
         <v>0</v>
       </c>
       <c r="AU27" s="3">
-        <f>+AA27-R27</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="AV27" s="3" t="s">
@@ -10296,37 +10296,37 @@
         <v>14</v>
       </c>
       <c r="O28" s="3">
-        <f>IF(I28="SFK Freight Forwarder",M28,M28+N28-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",O28,O28+P28-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R28" s="3">
-        <f>9+N28</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S28" s="3">
         <v>7</v>
       </c>
       <c r="T28" s="3">
-        <f>+R28+S28-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U28" s="3">
-        <f>+T28+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V28" s="3">
         <v>2</v>
       </c>
       <c r="W28" s="3">
-        <f>+U28+V28-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X28" s="3">
@@ -10339,7 +10339,7 @@
         <v>39</v>
       </c>
       <c r="AA28" s="6">
-        <f>+Z28+AB28-1</f>
+        <f t="shared" si="25"/>
         <v>44</v>
       </c>
       <c r="AB28" s="3">
@@ -10355,21 +10355,21 @@
         <v>34</v>
       </c>
       <c r="AF28" s="3">
-        <f>+AE28+AA28-1</f>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="AG28" s="6">
         <v>3</v>
       </c>
       <c r="AH28" s="6">
-        <f>+AF28+AG28</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="AI28" s="3">
         <v>0</v>
       </c>
       <c r="AJ28" s="3">
-        <f>+AI28+AH28</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AK28" s="3" t="s">
@@ -10379,36 +10379,36 @@
         <v>2</v>
       </c>
       <c r="AM28" s="3">
-        <f>+AJ28+AL28</f>
+        <f t="shared" si="7"/>
         <v>82</v>
       </c>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
       <c r="AO28" s="3">
-        <f>+AM28+AN28</f>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="AP28" s="3">
         <v>0</v>
       </c>
       <c r="AQ28" s="3">
-        <f>+AO28+AP28</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR28" s="3">
-        <f>+AQ28+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS28" s="3">
-        <f>+AR28+7+AT28</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AT28" s="3">
         <v>0</v>
       </c>
       <c r="AU28" s="3">
-        <f>+AA28-R28</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="AV28" s="3" t="s">
@@ -10468,37 +10468,37 @@
         <v>14</v>
       </c>
       <c r="O29" s="3">
-        <f>IF(I29="SFK Freight Forwarder",M29,M29+N29-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",O29,O29+P29-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <f>9+N29</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S29" s="3">
         <v>7</v>
       </c>
       <c r="T29" s="3">
-        <f>+R29+S29-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U29" s="3">
-        <f>+T29+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V29" s="3">
         <v>1</v>
       </c>
       <c r="W29" s="3">
-        <f>+U29+V29-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X29" s="3">
@@ -10511,7 +10511,7 @@
         <v>33</v>
       </c>
       <c r="AA29" s="6">
-        <f>+Z29+AB29-1</f>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="AB29" s="3">
@@ -10527,21 +10527,21 @@
         <v>53</v>
       </c>
       <c r="AF29" s="3">
-        <f>+AE29+AA29-1</f>
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
       <c r="AG29" s="6">
         <v>3</v>
       </c>
       <c r="AH29" s="6">
-        <f>+AF29+AG29</f>
+        <f t="shared" si="5"/>
         <v>90</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
-        <f>+AI29+AH29</f>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="AK29" s="3" t="s">
@@ -10551,36 +10551,36 @@
         <v>2</v>
       </c>
       <c r="AM29" s="3">
-        <f>+AJ29+AL29</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="AN29" s="3">
         <v>6</v>
       </c>
       <c r="AO29" s="3">
-        <f>+AM29+AN29</f>
+        <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
       <c r="AQ29" s="3">
-        <f>+AO29+AP29</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR29" s="3">
-        <f>+AQ29+7</f>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="AS29" s="3">
-        <f>+AR29+7+AT29</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AT29" s="3">
         <v>0</v>
       </c>
       <c r="AU29" s="3">
-        <f>+AA29-R29</f>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="AV29" s="3" t="s">
@@ -10640,37 +10640,37 @@
         <v>14</v>
       </c>
       <c r="O30" s="3">
-        <f>IF(I30="SFK Freight Forwarder",M30,M30+N30-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",O30,O30+P30-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f>9+N30</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S30" s="3">
         <v>7</v>
       </c>
       <c r="T30" s="3">
-        <f>+R30+S30-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U30" s="3">
-        <f>+T30+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V30" s="3">
         <v>2</v>
       </c>
       <c r="W30" s="3">
-        <f>+U30+V30-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X30" s="3">
@@ -10683,7 +10683,7 @@
         <v>34</v>
       </c>
       <c r="AA30" s="6">
-        <f>+Z30+AB30-1</f>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
       <c r="AB30" s="3">
@@ -10699,21 +10699,21 @@
         <v>31</v>
       </c>
       <c r="AF30" s="3">
-        <f>+AE30+AA30-1</f>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
       <c r="AG30" s="6">
         <v>3</v>
       </c>
       <c r="AH30" s="6">
-        <f>+AF30+AG30</f>
+        <f t="shared" si="5"/>
         <v>69</v>
       </c>
       <c r="AI30" s="3">
         <v>0</v>
       </c>
       <c r="AJ30" s="3">
-        <f>+AI30+AH30</f>
+        <f t="shared" si="6"/>
         <v>69</v>
       </c>
       <c r="AK30" s="3" t="s">
@@ -10723,36 +10723,36 @@
         <v>2</v>
       </c>
       <c r="AM30" s="3">
-        <f>+AJ30+AL30</f>
+        <f t="shared" si="7"/>
         <v>71</v>
       </c>
       <c r="AN30" s="3">
         <v>5</v>
       </c>
       <c r="AO30" s="3">
-        <f>+AM30+AN30</f>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="AP30" s="3">
         <v>1</v>
       </c>
       <c r="AQ30" s="3">
-        <f>+AO30+AP30</f>
+        <f t="shared" si="11"/>
         <v>77</v>
       </c>
       <c r="AR30" s="3">
-        <f>+AQ30+7</f>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AS30" s="3">
-        <f>+AR30+7+AT30</f>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="AT30" s="3">
         <v>0</v>
       </c>
       <c r="AU30" s="3">
-        <f>+AA30-R30</f>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="AV30" s="3" t="s">
@@ -10812,37 +10812,37 @@
         <v>14</v>
       </c>
       <c r="O31" s="3">
-        <f>IF(I31="SFK Freight Forwarder",M31,M31+N31-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",O31,O31+P31-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f>9+N31</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S31" s="3">
         <v>7</v>
       </c>
       <c r="T31" s="3">
-        <f>+R31+S31-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U31" s="3">
-        <f>+T31+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V31" s="3">
         <v>1</v>
       </c>
       <c r="W31" s="3">
-        <f>+U31+V31-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X31" s="3">
@@ -10855,7 +10855,7 @@
         <v>33</v>
       </c>
       <c r="AA31" s="6">
-        <f>+Z31+AB31-1</f>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
       <c r="AB31" s="3">
@@ -10871,21 +10871,21 @@
         <v>32</v>
       </c>
       <c r="AF31" s="3">
-        <f>+AE31+AA31-1</f>
+        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="AG31" s="6">
         <v>3</v>
       </c>
       <c r="AH31" s="6">
-        <f>+AF31+AG31</f>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="AI31" s="3">
         <v>0</v>
       </c>
       <c r="AJ31" s="3">
-        <f>+AI31+AH31</f>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="AK31" s="3" t="s">
@@ -10895,36 +10895,36 @@
         <v>4</v>
       </c>
       <c r="AM31" s="3">
-        <f>+AJ31+AL31</f>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="AN31" s="3">
         <v>3</v>
       </c>
       <c r="AO31" s="3">
-        <f>+AM31+AN31</f>
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="AP31" s="3">
         <v>0</v>
       </c>
       <c r="AQ31" s="3">
-        <f>+AO31+AP31</f>
+        <f t="shared" si="11"/>
         <v>77</v>
       </c>
       <c r="AR31" s="3">
-        <f>+AQ31+7</f>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AS31" s="3">
-        <f>+AR31+7+AT31</f>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="AT31" s="3">
         <v>0</v>
       </c>
       <c r="AU31" s="3">
-        <f>+AA31-R31</f>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="AV31" s="3" t="s">
@@ -10978,44 +10978,44 @@
         <v>7</v>
       </c>
       <c r="M32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",L32,9)</f>
+        <f t="shared" ref="M32:M43" si="28">+IF(I32="SFK Freight Forwarder",L32,9)</f>
         <v>9</v>
       </c>
       <c r="N32" s="3">
         <v>7</v>
       </c>
       <c r="O32" s="3">
-        <f>IF(I32="SFK Freight Forwarder",M32,M32+N32-1)</f>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="P32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",O32,O32+P32-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R32" s="3">
-        <f>9+N32</f>
+        <f t="shared" si="27"/>
         <v>16</v>
       </c>
       <c r="S32" s="3">
         <v>7</v>
       </c>
       <c r="T32" s="3">
-        <f>+R32+S32-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U32" s="3">
-        <f>+T32+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V32" s="3">
         <v>1</v>
       </c>
       <c r="W32" s="3">
-        <f>+U32+V32-1</f>
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
       <c r="X32" s="3">
@@ -11028,7 +11028,7 @@
         <v>25</v>
       </c>
       <c r="AA32" s="6">
-        <f>+Z32+AB32-1</f>
+        <f t="shared" si="25"/>
         <v>27</v>
       </c>
       <c r="AB32" s="3">
@@ -11044,21 +11044,21 @@
         <v>46</v>
       </c>
       <c r="AF32" s="3">
-        <f>+AE32+AA32-1</f>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="AG32" s="6">
         <v>3</v>
       </c>
       <c r="AH32" s="6">
-        <f>+AF32+AG32</f>
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
       <c r="AJ32" s="3">
-        <f>+AI32+AH32</f>
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
       <c r="AK32" s="3" t="s">
@@ -11068,36 +11068,36 @@
         <v>9</v>
       </c>
       <c r="AM32" s="3">
-        <f>+AJ32+AL32</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="AN32" s="3">
         <v>2</v>
       </c>
       <c r="AO32" s="3">
-        <f>+AM32+AN32</f>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="AP32" s="3">
         <v>5</v>
       </c>
       <c r="AQ32" s="3">
-        <f>+AO32+AP32</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR32" s="3">
-        <f>+AQ32+7</f>
+        <f t="shared" si="17"/>
         <v>98</v>
       </c>
       <c r="AS32" s="3">
-        <f>+AR32+7+AT32</f>
+        <f t="shared" si="9"/>
         <v>115</v>
       </c>
       <c r="AT32" s="3">
         <v>10</v>
       </c>
       <c r="AU32" s="3">
-        <f>+AA32-R32</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AV32" s="3" t="s">
@@ -11151,44 +11151,44 @@
         <v>7</v>
       </c>
       <c r="M33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",L33,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N33" s="3">
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f>IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R33" s="3">
-        <f>9+N33</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S33" s="3">
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f>+R33+S33-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U33" s="3">
-        <f>+T33+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V33" s="3">
         <v>2</v>
       </c>
       <c r="W33" s="3">
-        <f>+U33+V33-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X33" s="3">
@@ -11201,7 +11201,7 @@
         <v>33</v>
       </c>
       <c r="AA33" s="6">
-        <f>+Z33+AB33-1</f>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="AB33" s="3">
@@ -11217,21 +11217,21 @@
         <v>68</v>
       </c>
       <c r="AF33" s="3">
-        <f>+AE33+AA33-1</f>
+        <f t="shared" si="4"/>
         <v>102</v>
       </c>
       <c r="AG33" s="6">
         <v>3</v>
       </c>
       <c r="AH33" s="6">
-        <f>+AF33+AG33</f>
+        <f t="shared" si="5"/>
         <v>105</v>
       </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
-        <f>+AI33+AH33</f>
+        <f t="shared" si="6"/>
         <v>105</v>
       </c>
       <c r="AK33" s="3" t="s">
@@ -11241,36 +11241,36 @@
         <v>9</v>
       </c>
       <c r="AM33" s="3">
-        <f>+AJ33+AL33</f>
+        <f t="shared" si="7"/>
         <v>114</v>
       </c>
       <c r="AN33" s="3">
         <v>2</v>
       </c>
       <c r="AO33" s="3">
-        <f>+AM33+AN33</f>
+        <f t="shared" si="8"/>
         <v>116</v>
       </c>
       <c r="AP33" s="3">
         <v>3</v>
       </c>
       <c r="AQ33" s="3">
-        <f>+AO33+AP33</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR33" s="3">
-        <f>+AQ33+7</f>
+        <f t="shared" si="17"/>
         <v>126</v>
       </c>
       <c r="AS33" s="3">
-        <f>+AR33+7+AT33</f>
+        <f t="shared" si="9"/>
         <v>143</v>
       </c>
       <c r="AT33" s="3">
         <v>10</v>
       </c>
       <c r="AU33" s="3">
-        <f>+AA33-R33</f>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="AV33" s="3" t="s">
@@ -11324,44 +11324,44 @@
         <v>7</v>
       </c>
       <c r="M34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",L34,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N34" s="3">
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f>IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q65" si="29">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>26</v>
       </c>
       <c r="R34" s="3">
-        <f>9+N34</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S34" s="3">
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f>+R34+S34-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U34" s="3">
-        <f>+T34+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V34" s="3">
         <v>3</v>
       </c>
       <c r="W34" s="3">
-        <f>+U34+V34-1</f>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="X34" s="3">
@@ -11374,7 +11374,7 @@
         <v>33</v>
       </c>
       <c r="AA34" s="6">
-        <f>+Z34+AB34-1</f>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="AB34" s="3">
@@ -11390,21 +11390,21 @@
         <v>75</v>
       </c>
       <c r="AF34" s="3">
-        <f>+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF65" si="30">+AE34+AA34-1</f>
         <v>109</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f>+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH65" si="31">+AF34+AG34</f>
         <v>112</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f>+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ65" si="32">+AI34+AH34</f>
         <v>112</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -11414,36 +11414,36 @@
         <v>9</v>
       </c>
       <c r="AM34" s="3">
-        <f>+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM65" si="33">+AJ34+AL34</f>
         <v>121</v>
       </c>
       <c r="AN34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3">
-        <f>+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO65" si="34">+AM34+AN34</f>
         <v>123</v>
       </c>
       <c r="AP34" s="3">
         <v>3</v>
       </c>
       <c r="AQ34" s="3">
-        <f>+AO34+AP34</f>
+        <f t="shared" si="11"/>
         <v>126</v>
       </c>
       <c r="AR34" s="3">
-        <f>+AQ34+7</f>
+        <f t="shared" si="17"/>
         <v>133</v>
       </c>
       <c r="AS34" s="3">
-        <f>+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS65" si="35">+AR34+7+AT34</f>
         <v>150</v>
       </c>
       <c r="AT34" s="3">
         <v>10</v>
       </c>
       <c r="AU34" s="3">
-        <f>+AA34-R34</f>
+        <f t="shared" ref="AU34:AU55" si="36">+AA34-R34</f>
         <v>12</v>
       </c>
       <c r="AV34" s="3" t="s">
@@ -11497,44 +11497,44 @@
         <v>7</v>
       </c>
       <c r="M35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",L35,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N35" s="3">
         <v>14</v>
       </c>
       <c r="O35" s="3">
-        <f>IF(I35="SFK Freight Forwarder",M35,M35+N35-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",O35,O35+P35-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R35" s="3">
-        <f>9+N35</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S35" s="3">
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f>+R35+S35-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U35" s="3">
-        <f>+T35+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V35" s="3">
         <v>4</v>
       </c>
       <c r="W35" s="3">
-        <f>+U35+V35-1</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="X35" s="3">
@@ -11562,21 +11562,21 @@
         <v>33</v>
       </c>
       <c r="AF35" s="3">
-        <f>+AE35+AA35-1</f>
+        <f t="shared" si="30"/>
         <v>72</v>
       </c>
       <c r="AG35" s="6">
         <v>3</v>
       </c>
       <c r="AH35" s="6">
-        <f>+AF35+AG35</f>
+        <f t="shared" si="31"/>
         <v>75</v>
       </c>
       <c r="AI35" s="3">
         <v>0</v>
       </c>
       <c r="AJ35" s="3">
-        <f>+AI35+AH35</f>
+        <f t="shared" si="32"/>
         <v>75</v>
       </c>
       <c r="AK35" s="28" t="s">
@@ -11586,36 +11586,36 @@
         <v>9</v>
       </c>
       <c r="AM35" s="3">
-        <f>+AJ35+AL35</f>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
-        <f>+AM35+AN35</f>
+        <f t="shared" si="34"/>
         <v>86</v>
       </c>
       <c r="AP35" s="3">
         <v>5</v>
       </c>
       <c r="AQ35" s="3">
-        <f>+AO35+AP35</f>
+        <f t="shared" ref="AQ35:AQ66" si="37">+AO35+AP35</f>
         <v>91</v>
       </c>
       <c r="AR35" s="3">
-        <f>+AQ35+7</f>
+        <f t="shared" si="17"/>
         <v>98</v>
       </c>
       <c r="AS35" s="3">
-        <f>+AR35+7+AT35</f>
+        <f t="shared" si="35"/>
         <v>121</v>
       </c>
       <c r="AT35" s="3">
         <v>16</v>
       </c>
       <c r="AU35" s="3">
-        <f>+AA35-R35</f>
+        <f t="shared" si="36"/>
         <v>17</v>
       </c>
       <c r="AV35" s="3" t="s">
@@ -11669,44 +11669,44 @@
         <v>7</v>
       </c>
       <c r="M36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",L36,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N36" s="3">
         <v>14</v>
       </c>
       <c r="O36" s="3">
-        <f>IF(I36="SFK Freight Forwarder",M36,M36+N36-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",O36,O36+P36-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R36" s="3">
-        <f>9+N36</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S36" s="3">
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f>+R36+S36-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U36" s="3">
-        <f>+T36+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V36" s="3">
         <v>1</v>
       </c>
       <c r="W36" s="3">
-        <f>+U36+V36-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X36" s="3">
@@ -11720,7 +11720,7 @@
         <v>37</v>
       </c>
       <c r="AA36" s="6">
-        <f>+Z36+AB36-1</f>
+        <f t="shared" ref="AA36:AA43" si="38">+Z36+AB36-1</f>
         <v>39</v>
       </c>
       <c r="AB36" s="3">
@@ -11736,21 +11736,21 @@
         <v>26</v>
       </c>
       <c r="AF36" s="3">
-        <f>+AE36+AA36-1</f>
+        <f t="shared" si="30"/>
         <v>64</v>
       </c>
       <c r="AG36" s="6">
         <v>3</v>
       </c>
       <c r="AH36" s="6">
-        <f>+AF36+AG36</f>
+        <f t="shared" si="31"/>
         <v>67</v>
       </c>
       <c r="AI36" s="3">
         <v>0</v>
       </c>
       <c r="AJ36" s="3">
-        <f>+AI36+AH36</f>
+        <f t="shared" si="32"/>
         <v>67</v>
       </c>
       <c r="AK36" s="3" t="s">
@@ -11760,36 +11760,36 @@
         <v>9</v>
       </c>
       <c r="AM36" s="3">
-        <f>+AJ36+AL36</f>
+        <f t="shared" si="33"/>
         <v>76</v>
       </c>
       <c r="AN36" s="3">
         <v>2</v>
       </c>
       <c r="AO36" s="3">
-        <f>+AM36+AN36</f>
+        <f t="shared" si="34"/>
         <v>78</v>
       </c>
       <c r="AP36" s="3">
         <v>6</v>
       </c>
       <c r="AQ36" s="3">
-        <f>+AO36+AP36</f>
+        <f t="shared" si="37"/>
         <v>84</v>
       </c>
       <c r="AR36" s="3">
-        <f>+AQ36+7</f>
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
       <c r="AS36" s="3">
-        <f>+AR36+7+AT36</f>
+        <f t="shared" si="35"/>
         <v>112</v>
       </c>
       <c r="AT36" s="3">
         <v>14</v>
       </c>
       <c r="AU36" s="3">
-        <f>+AA36-R36</f>
+        <f t="shared" si="36"/>
         <v>16</v>
       </c>
       <c r="AV36" s="3" t="s">
@@ -11843,44 +11843,44 @@
         <v>7</v>
       </c>
       <c r="M37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",L37,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N37" s="3">
         <v>14</v>
       </c>
       <c r="O37" s="3">
-        <f>IF(I37="SFK Freight Forwarder",M37,M37+N37-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",O37,O37+P37-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R37" s="3">
-        <f>9+N37</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S37" s="3">
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f>+R37+S37-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U37" s="3">
-        <f>+T37+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V37" s="3">
         <v>4</v>
       </c>
       <c r="W37" s="3">
-        <f>+U37+V37-1</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="X37" s="3">
@@ -11893,7 +11893,7 @@
         <v>33</v>
       </c>
       <c r="AA37" s="6">
-        <f>+Z37+AB37-1</f>
+        <f t="shared" si="38"/>
         <v>35</v>
       </c>
       <c r="AB37" s="3">
@@ -11909,21 +11909,21 @@
         <v>44</v>
       </c>
       <c r="AF37" s="3">
-        <f>+AE37+AA37-1</f>
+        <f t="shared" si="30"/>
         <v>78</v>
       </c>
       <c r="AG37" s="6">
         <v>3</v>
       </c>
       <c r="AH37" s="6">
-        <f>+AF37+AG37</f>
+        <f t="shared" si="31"/>
         <v>81</v>
       </c>
       <c r="AI37" s="3">
         <v>0</v>
       </c>
       <c r="AJ37" s="3">
-        <f>+AI37+AH37</f>
+        <f t="shared" si="32"/>
         <v>81</v>
       </c>
       <c r="AK37" s="3" t="s">
@@ -11933,36 +11933,36 @@
         <v>9</v>
       </c>
       <c r="AM37" s="3">
-        <f>+AJ37+AL37</f>
+        <f t="shared" si="33"/>
         <v>90</v>
       </c>
       <c r="AN37" s="3">
         <v>2</v>
       </c>
       <c r="AO37" s="3">
-        <f>+AM37+AN37</f>
+        <f t="shared" si="34"/>
         <v>92</v>
       </c>
       <c r="AP37" s="3">
         <v>6</v>
       </c>
       <c r="AQ37" s="3">
-        <f>+AO37+AP37</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR37" s="3">
-        <f>+AQ37+7</f>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="AS37" s="3">
-        <f>+AR37+7+AT37</f>
+        <f t="shared" si="35"/>
         <v>121</v>
       </c>
       <c r="AT37" s="3">
         <v>9</v>
       </c>
       <c r="AU37" s="3">
-        <f>+AA37-R37</f>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="AV37" s="3" t="s">
@@ -12016,44 +12016,44 @@
         <v>7</v>
       </c>
       <c r="M38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",L38,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N38" s="3">
         <v>7</v>
       </c>
       <c r="O38" s="3">
-        <f>IF(I38="SFK Freight Forwarder",M38,M38+N38-1)</f>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="P38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",O38,O38+P38-1)</f>
+        <f t="shared" si="29"/>
         <v>19</v>
       </c>
       <c r="R38" s="3">
-        <f>9+N38</f>
+        <f t="shared" si="27"/>
         <v>16</v>
       </c>
       <c r="S38" s="3">
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f>+R38+S38-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U38" s="3">
-        <f>+T38+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V38" s="3">
         <v>4</v>
       </c>
       <c r="W38" s="3">
-        <f>+U38+V38-1</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="X38" s="3">
@@ -12066,7 +12066,7 @@
         <v>31</v>
       </c>
       <c r="AA38" s="6">
-        <f>+Z38+AB38-1</f>
+        <f t="shared" si="38"/>
         <v>33</v>
       </c>
       <c r="AB38" s="3">
@@ -12082,21 +12082,21 @@
         <v>27</v>
       </c>
       <c r="AF38" s="3">
-        <f>+AE38+AA38-1</f>
+        <f t="shared" si="30"/>
         <v>59</v>
       </c>
       <c r="AG38" s="6">
         <v>3</v>
       </c>
       <c r="AH38" s="6">
-        <f>+AF38+AG38</f>
+        <f t="shared" si="31"/>
         <v>62</v>
       </c>
       <c r="AI38" s="3">
         <v>0</v>
       </c>
       <c r="AJ38" s="3">
-        <f>+AI38+AH38</f>
+        <f t="shared" si="32"/>
         <v>62</v>
       </c>
       <c r="AK38" s="3" t="s">
@@ -12106,36 +12106,36 @@
         <v>9</v>
       </c>
       <c r="AM38" s="3">
-        <f>+AJ38+AL38</f>
+        <f t="shared" si="33"/>
         <v>71</v>
       </c>
       <c r="AN38" s="3">
         <v>9</v>
       </c>
       <c r="AO38" s="3">
-        <f>+AM38+AN38</f>
+        <f t="shared" si="34"/>
         <v>80</v>
       </c>
       <c r="AP38" s="3">
         <v>4</v>
       </c>
       <c r="AQ38" s="3">
-        <f>+AO38+AP38</f>
+        <f t="shared" si="37"/>
         <v>84</v>
       </c>
       <c r="AR38" s="3">
-        <f>+AQ38+7</f>
+        <f t="shared" ref="AR38:AR69" si="39">+AQ38+7</f>
         <v>91</v>
       </c>
       <c r="AS38" s="3">
-        <f>+AR38+7+AT38</f>
+        <f t="shared" si="35"/>
         <v>111</v>
       </c>
       <c r="AT38" s="3">
         <v>13</v>
       </c>
       <c r="AU38" s="3">
-        <f>+AA38-R38</f>
+        <f t="shared" si="36"/>
         <v>17</v>
       </c>
       <c r="AV38" s="3" t="s">
@@ -12189,44 +12189,44 @@
         <v>2</v>
       </c>
       <c r="M39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",L39,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N39" s="3">
         <v>14</v>
       </c>
       <c r="O39" s="3">
-        <f>IF(I39="SFK Freight Forwarder",M39,M39+N39-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",O39,O39+P39-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R39" s="3">
-        <f>9+N39</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S39" s="3">
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f>+R39+S39-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U39" s="3">
-        <f>+T39+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V39" s="3">
         <v>3</v>
       </c>
       <c r="W39" s="3">
-        <f>+U39+V39-1</f>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="X39" s="3">
@@ -12239,7 +12239,7 @@
         <v>37</v>
       </c>
       <c r="AA39" s="6">
-        <f>+Z39+AB39-1</f>
+        <f t="shared" si="38"/>
         <v>39</v>
       </c>
       <c r="AB39" s="3">
@@ -12255,21 +12255,21 @@
         <v>46</v>
       </c>
       <c r="AF39" s="3">
-        <f>+AE39+AA39-1</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AG39" s="6">
         <v>3</v>
       </c>
       <c r="AH39" s="6">
-        <f>+AF39+AG39</f>
+        <f t="shared" si="31"/>
         <v>87</v>
       </c>
       <c r="AI39" s="3">
         <v>0</v>
       </c>
       <c r="AJ39" s="3">
-        <f>+AI39+AH39</f>
+        <f t="shared" si="32"/>
         <v>87</v>
       </c>
       <c r="AK39" s="3" t="s">
@@ -12279,36 +12279,36 @@
         <v>9</v>
       </c>
       <c r="AM39" s="3">
-        <f>+AJ39+AL39</f>
+        <f t="shared" si="33"/>
         <v>96</v>
       </c>
       <c r="AN39" s="3">
         <v>2</v>
       </c>
       <c r="AO39" s="3">
-        <f>+AM39+AN39</f>
+        <f t="shared" si="34"/>
         <v>98</v>
       </c>
       <c r="AP39" s="3">
         <v>0</v>
       </c>
       <c r="AQ39" s="3">
-        <f>+AO39+AP39</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR39" s="3">
-        <f>+AQ39+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS39" s="3">
-        <f>+AR39+7+AT39</f>
+        <f t="shared" si="35"/>
         <v>126</v>
       </c>
       <c r="AT39" s="3">
         <v>14</v>
       </c>
       <c r="AU39" s="3">
-        <f>+AA39-R39</f>
+        <f t="shared" si="36"/>
         <v>16</v>
       </c>
       <c r="AV39" s="3" t="s">
@@ -12362,44 +12362,44 @@
         <v>7</v>
       </c>
       <c r="M40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",L40,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N40" s="3">
         <v>7</v>
       </c>
       <c r="O40" s="3">
-        <f>IF(I40="SFK Freight Forwarder",M40,M40+N40-1)</f>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="P40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",O40,O40+P40-1)</f>
+        <f t="shared" si="29"/>
         <v>19</v>
       </c>
       <c r="R40" s="3">
-        <f>9+N40</f>
+        <f t="shared" si="27"/>
         <v>16</v>
       </c>
       <c r="S40" s="3">
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f>+R40+S40-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U40" s="3">
-        <f>+T40+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V40" s="3">
         <v>2</v>
       </c>
       <c r="W40" s="3">
-        <f>+U40+V40-1</f>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="X40" s="3">
@@ -12412,7 +12412,7 @@
         <v>31</v>
       </c>
       <c r="AA40" s="6">
-        <f>+Z40+AB40-1</f>
+        <f t="shared" si="38"/>
         <v>33</v>
       </c>
       <c r="AB40" s="3">
@@ -12428,21 +12428,21 @@
         <v>21</v>
       </c>
       <c r="AF40" s="3">
-        <f>+AE40+AA40-1</f>
+        <f t="shared" si="30"/>
         <v>53</v>
       </c>
       <c r="AG40" s="6">
         <v>3</v>
       </c>
       <c r="AH40" s="6">
-        <f>+AF40+AG40</f>
+        <f t="shared" si="31"/>
         <v>56</v>
       </c>
       <c r="AI40" s="3">
         <v>0</v>
       </c>
       <c r="AJ40" s="3">
-        <f>+AI40+AH40</f>
+        <f t="shared" si="32"/>
         <v>56</v>
       </c>
       <c r="AK40" s="3" t="s">
@@ -12452,36 +12452,36 @@
         <v>9</v>
       </c>
       <c r="AM40" s="3">
-        <f>+AJ40+AL40</f>
+        <f t="shared" si="33"/>
         <v>65</v>
       </c>
       <c r="AN40" s="3">
         <v>2</v>
       </c>
       <c r="AO40" s="3">
-        <f>+AM40+AN40</f>
+        <f t="shared" si="34"/>
         <v>67</v>
       </c>
       <c r="AP40" s="3">
         <v>3</v>
       </c>
       <c r="AQ40" s="3">
-        <f>+AO40+AP40</f>
+        <f t="shared" si="37"/>
         <v>70</v>
       </c>
       <c r="AR40" s="3">
-        <f>+AQ40+7</f>
+        <f t="shared" si="39"/>
         <v>77</v>
       </c>
       <c r="AS40" s="3">
-        <f>+AR40+7+AT40</f>
+        <f t="shared" si="35"/>
         <v>98</v>
       </c>
       <c r="AT40" s="3">
         <v>14</v>
       </c>
       <c r="AU40" s="3">
-        <f>+AA40-R40</f>
+        <f t="shared" si="36"/>
         <v>17</v>
       </c>
       <c r="AV40" s="3" t="s">
@@ -12535,43 +12535,43 @@
         <v>7</v>
       </c>
       <c r="M41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",L41,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N41" s="3">
         <v>14</v>
       </c>
       <c r="O41" s="3">
-        <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P41" s="3">
         <v>5</v>
       </c>
       <c r="Q41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R41" s="3">
-        <f>9+N41</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f>+R41+S41-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U41" s="3">
-        <f>+T41+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f>+U41+V41-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X41" s="3">
@@ -12584,7 +12584,7 @@
         <v>35</v>
       </c>
       <c r="AA41" s="6">
-        <f>+Z41+AB41-1</f>
+        <f t="shared" si="38"/>
         <v>37</v>
       </c>
       <c r="AB41" s="3">
@@ -12600,21 +12600,21 @@
         <v>40</v>
       </c>
       <c r="AF41" s="3">
-        <f>+AE41+AA41-1</f>
+        <f t="shared" si="30"/>
         <v>76</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
-        <f>+AF41+AG41</f>
+        <f t="shared" si="31"/>
         <v>79</v>
       </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
-        <f>+AI41+AH41</f>
+        <f t="shared" si="32"/>
         <v>79</v>
       </c>
       <c r="AK41" s="3" t="s">
@@ -12624,36 +12624,36 @@
         <v>9</v>
       </c>
       <c r="AM41" s="3">
-        <f>+AJ41+AL41</f>
+        <f t="shared" si="33"/>
         <v>88</v>
       </c>
       <c r="AN41" s="3">
         <v>10</v>
       </c>
       <c r="AO41" s="3">
-        <f>+AM41+AN41</f>
+        <f t="shared" si="34"/>
         <v>98</v>
       </c>
       <c r="AP41" s="3">
         <v>0</v>
       </c>
       <c r="AQ41" s="3">
-        <f>+AO41+AP41</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR41" s="3">
-        <f>+AQ41+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS41" s="3">
-        <f>+AR41+7+AT41</f>
+        <f t="shared" si="35"/>
         <v>129</v>
       </c>
       <c r="AT41" s="3">
         <v>17</v>
       </c>
       <c r="AU41" s="3">
-        <f>+AA41-R41</f>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AV41" s="3" t="s">
@@ -12707,44 +12707,44 @@
         <v>7</v>
       </c>
       <c r="M42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",L42,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N42" s="3">
         <v>14</v>
       </c>
       <c r="O42" s="3">
-        <f>IF(I42="SFK Freight Forwarder",M42,M42+N42-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P42:P55" si="40">+IF(I42="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",O42,O42+P42-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R42" s="3">
-        <f>9+N42</f>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f>+R42+S42-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U42" s="3">
-        <f>+T42+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
-        <f>+U42+V42-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X42" s="3">
@@ -12757,7 +12757,7 @@
         <v>33</v>
       </c>
       <c r="AA42" s="6">
-        <f>+Z42+AB42-1</f>
+        <f t="shared" si="38"/>
         <v>35</v>
       </c>
       <c r="AB42" s="3">
@@ -12773,21 +12773,21 @@
         <v>43</v>
       </c>
       <c r="AF42" s="3">
-        <f>+AE42+AA42-1</f>
+        <f t="shared" si="30"/>
         <v>77</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
-        <f>+AF42+AG42</f>
+        <f t="shared" si="31"/>
         <v>80</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
-        <f>+AI42+AH42</f>
+        <f t="shared" si="32"/>
         <v>80</v>
       </c>
       <c r="AK42" s="3" t="s">
@@ -12797,36 +12797,36 @@
         <v>9</v>
       </c>
       <c r="AM42" s="3">
-        <f>+AJ42+AL42</f>
+        <f t="shared" si="33"/>
         <v>89</v>
       </c>
       <c r="AN42" s="3">
         <v>2</v>
       </c>
       <c r="AO42" s="3">
-        <f>+AM42+AN42</f>
+        <f t="shared" si="34"/>
         <v>91</v>
       </c>
       <c r="AP42" s="3">
         <v>0</v>
       </c>
       <c r="AQ42" s="3">
-        <f>+AO42+AP42</f>
+        <f t="shared" si="37"/>
         <v>91</v>
       </c>
       <c r="AR42" s="3">
-        <f>+AQ42+7</f>
+        <f t="shared" si="39"/>
         <v>98</v>
       </c>
       <c r="AS42" s="3">
-        <f>+AR42+7+AT42</f>
+        <f t="shared" si="35"/>
         <v>122</v>
       </c>
       <c r="AT42" s="3">
         <v>17</v>
       </c>
       <c r="AU42" s="3">
-        <f>+AA42-R42</f>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="AV42" s="3" t="s">
@@ -12880,44 +12880,44 @@
         <v>2</v>
       </c>
       <c r="M43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",L43,9)</f>
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
       <c r="N43" s="3">
         <v>21</v>
       </c>
       <c r="O43" s="3">
-        <f>IF(I43="SFK Freight Forwarder",M43,M43+N43-1)</f>
+        <f t="shared" si="26"/>
         <v>29</v>
       </c>
       <c r="P43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",O43,O43+P43-1)</f>
+        <f t="shared" si="29"/>
         <v>33</v>
       </c>
       <c r="R43" s="3">
-        <f>9+N43</f>
+        <f t="shared" si="27"/>
         <v>30</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f>+R43+S43-1</f>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="U43" s="3">
-        <f>+T43+1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="V43" s="3">
         <v>1</v>
       </c>
       <c r="W43" s="3">
-        <f>+U43+V43-1</f>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="X43" s="3">
@@ -12930,7 +12930,7 @@
         <v>37</v>
       </c>
       <c r="AA43" s="6">
-        <f>+Z43+AB43-1</f>
+        <f t="shared" si="38"/>
         <v>39</v>
       </c>
       <c r="AB43" s="3">
@@ -12946,21 +12946,21 @@
         <v>46</v>
       </c>
       <c r="AF43" s="3">
-        <f>+AE43+AA43-1</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
-        <f>+AF43+AG43</f>
+        <f t="shared" si="31"/>
         <v>87</v>
       </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
       <c r="AJ43" s="3">
-        <f>+AI43+AH43</f>
+        <f t="shared" si="32"/>
         <v>87</v>
       </c>
       <c r="AK43" s="3" t="s">
@@ -12970,36 +12970,36 @@
         <v>11</v>
       </c>
       <c r="AM43" s="3">
-        <f>+AJ43+AL43</f>
+        <f t="shared" si="33"/>
         <v>98</v>
       </c>
       <c r="AN43" s="3">
         <v>3</v>
       </c>
       <c r="AO43" s="3">
-        <f>+AM43+AN43</f>
+        <f t="shared" si="34"/>
         <v>101</v>
       </c>
       <c r="AP43" s="3">
         <v>4</v>
       </c>
       <c r="AQ43" s="3">
-        <f>+AO43+AP43</f>
+        <f t="shared" si="37"/>
         <v>105</v>
       </c>
       <c r="AR43" s="3">
-        <f>+AQ43+7</f>
+        <f t="shared" si="39"/>
         <v>112</v>
       </c>
       <c r="AS43" s="3">
-        <f>+AR43+7+AT43</f>
+        <f t="shared" si="35"/>
         <v>119</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
-        <f>+AA43-R43</f>
+        <f t="shared" si="36"/>
         <v>9</v>
       </c>
       <c r="AV43" s="3" t="s">
@@ -13059,15 +13059,15 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <f>IF(I44="SFK Freight Forwarder",M44,M44+N44-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",O44,O44+P44-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R44" s="3">
@@ -13077,18 +13077,18 @@
         <v>7</v>
       </c>
       <c r="T44" s="3">
-        <f>+R44+S44-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U44" s="3">
-        <f>+T44+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V44" s="3">
         <v>8</v>
       </c>
       <c r="W44" s="3">
-        <f>+U44+V44-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X44" s="3">
@@ -13116,21 +13116,21 @@
         <v>38</v>
       </c>
       <c r="AF44" s="3">
-        <f>+AE44+AA44-1</f>
+        <f t="shared" si="30"/>
         <v>72</v>
       </c>
       <c r="AG44" s="6">
         <v>3</v>
       </c>
       <c r="AH44" s="6">
-        <f>+AF44+AG44</f>
+        <f t="shared" si="31"/>
         <v>75</v>
       </c>
       <c r="AI44" s="3">
         <v>0</v>
       </c>
       <c r="AJ44" s="3">
-        <f>+AI44+AH44</f>
+        <f t="shared" si="32"/>
         <v>75</v>
       </c>
       <c r="AK44" s="3" t="s">
@@ -13140,36 +13140,36 @@
         <v>10</v>
       </c>
       <c r="AM44" s="3">
-        <f>+AJ44+AL44</f>
+        <f t="shared" si="33"/>
         <v>85</v>
       </c>
       <c r="AN44" s="3">
         <v>6</v>
       </c>
       <c r="AO44" s="3">
-        <f>+AM44+AN44</f>
+        <f t="shared" si="34"/>
         <v>91</v>
       </c>
       <c r="AP44" s="3">
         <v>0</v>
       </c>
       <c r="AQ44" s="3">
-        <f>+AO44+AP44</f>
+        <f t="shared" si="37"/>
         <v>91</v>
       </c>
       <c r="AR44" s="3">
-        <f>+AQ44+7</f>
+        <f t="shared" si="39"/>
         <v>98</v>
       </c>
       <c r="AS44" s="3">
-        <f>+AR44+7+AT44</f>
+        <f t="shared" si="35"/>
         <v>105</v>
       </c>
       <c r="AT44" s="3">
         <v>0</v>
       </c>
       <c r="AU44" s="3">
-        <f>+AA44-R44</f>
+        <f t="shared" si="36"/>
         <v>19</v>
       </c>
       <c r="AV44" s="3" t="s">
@@ -13229,37 +13229,37 @@
         <v>7</v>
       </c>
       <c r="O45" s="3">
-        <f>IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <f>9+N45</f>
+        <f t="shared" ref="R45:R55" si="41">9+N45</f>
         <v>16</v>
       </c>
       <c r="S45" s="3">
         <v>7</v>
       </c>
       <c r="T45" s="3">
-        <f>+R45+S45-1</f>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="U45" s="3">
-        <f>+T45+1</f>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
       <c r="V45" s="3">
         <v>8</v>
       </c>
       <c r="W45" s="3">
-        <f>+U45+V45-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X45" s="3">
@@ -13272,7 +13272,7 @@
         <v>36</v>
       </c>
       <c r="AA45" s="6">
-        <f>+Z45+AB45-1</f>
+        <f t="shared" ref="AA45:AA55" si="42">+Z45+AB45-1</f>
         <v>38</v>
       </c>
       <c r="AB45" s="3">
@@ -13288,21 +13288,21 @@
         <v>16</v>
       </c>
       <c r="AF45" s="3">
-        <f>+AE45+AA45-1</f>
+        <f t="shared" si="30"/>
         <v>53</v>
       </c>
       <c r="AG45" s="6">
         <v>3</v>
       </c>
       <c r="AH45" s="6">
-        <f>+AF45+AG45</f>
+        <f t="shared" si="31"/>
         <v>56</v>
       </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
       <c r="AJ45" s="3">
-        <f>+AI45+AH45</f>
+        <f t="shared" si="32"/>
         <v>56</v>
       </c>
       <c r="AK45" s="3" t="s">
@@ -13312,36 +13312,36 @@
         <v>11</v>
       </c>
       <c r="AM45" s="3">
-        <f>+AJ45+AL45</f>
+        <f t="shared" si="33"/>
         <v>67</v>
       </c>
       <c r="AN45" s="3">
         <v>3</v>
       </c>
       <c r="AO45" s="3">
-        <f>+AM45+AN45</f>
+        <f t="shared" si="34"/>
         <v>70</v>
       </c>
       <c r="AP45" s="3">
         <v>0</v>
       </c>
       <c r="AQ45" s="3">
-        <f>+AO45+AP45</f>
+        <f t="shared" si="37"/>
         <v>70</v>
       </c>
       <c r="AR45" s="3">
-        <f>+AQ45+7</f>
+        <f t="shared" si="39"/>
         <v>77</v>
       </c>
       <c r="AS45" s="3">
-        <f>+AR45+7+AT45</f>
+        <f t="shared" si="35"/>
         <v>84</v>
       </c>
       <c r="AT45" s="3">
         <v>0</v>
       </c>
       <c r="AU45" s="3">
-        <f>+AA45-R45</f>
+        <f t="shared" si="36"/>
         <v>22</v>
       </c>
       <c r="AV45" s="3" t="s">
@@ -13401,37 +13401,37 @@
         <v>14</v>
       </c>
       <c r="O46" s="3">
-        <f>IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <f>9+N46</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S46" s="3">
         <v>7</v>
       </c>
       <c r="T46" s="3">
-        <f>+R46+S46-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U46" s="3">
-        <f>+T46+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V46" s="3">
         <v>1</v>
       </c>
       <c r="W46" s="3">
-        <f>+U46+V46-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X46" s="3">
@@ -13446,7 +13446,7 @@
         <v>33</v>
       </c>
       <c r="AA46" s="6">
-        <f>+Z46+AB46-1</f>
+        <f t="shared" si="42"/>
         <v>35</v>
       </c>
       <c r="AB46" s="3">
@@ -13462,21 +13462,21 @@
         <v>49</v>
       </c>
       <c r="AF46" s="3">
-        <f>+AE46+AA46-1</f>
+        <f t="shared" si="30"/>
         <v>83</v>
       </c>
       <c r="AG46" s="6">
         <v>3</v>
       </c>
       <c r="AH46" s="6">
-        <f>+AF46+AG46</f>
+        <f t="shared" si="31"/>
         <v>86</v>
       </c>
       <c r="AI46" s="3">
         <v>0</v>
       </c>
       <c r="AJ46" s="3">
-        <f>+AI46+AH46</f>
+        <f t="shared" si="32"/>
         <v>86</v>
       </c>
       <c r="AK46" s="3" t="s">
@@ -13486,36 +13486,36 @@
         <v>10</v>
       </c>
       <c r="AM46" s="3">
-        <f>+AJ46+AL46</f>
+        <f t="shared" si="33"/>
         <v>96</v>
       </c>
       <c r="AN46" s="3">
         <v>1</v>
       </c>
       <c r="AO46" s="3">
-        <f>+AM46+AN46</f>
+        <f t="shared" si="34"/>
         <v>97</v>
       </c>
       <c r="AP46" s="3">
         <v>1</v>
       </c>
       <c r="AQ46" s="3">
-        <f>+AO46+AP46</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR46" s="3">
-        <f>+AQ46+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS46" s="3">
-        <f>+AR46+7+AT46</f>
+        <f t="shared" si="35"/>
         <v>112</v>
       </c>
       <c r="AT46" s="3">
         <v>0</v>
       </c>
       <c r="AU46" s="3">
-        <f>+AA46-R46</f>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="AV46" s="3" t="s">
@@ -13575,37 +13575,37 @@
         <v>14</v>
       </c>
       <c r="O47" s="3">
-        <f>IF(I47="SFK Freight Forwarder",M47,M47+N47-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",O47,O47+P47-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <f>9+N47</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S47" s="3">
         <v>7</v>
       </c>
       <c r="T47" s="3">
-        <f>+R47+S47-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f>+T47+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V47" s="3">
         <v>1</v>
       </c>
       <c r="W47" s="3">
-        <f>+U47+V47-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X47" s="3">
@@ -13618,7 +13618,7 @@
         <v>33</v>
       </c>
       <c r="AA47" s="6">
-        <f>+Z47+AB47-1</f>
+        <f t="shared" si="42"/>
         <v>36</v>
       </c>
       <c r="AB47" s="3">
@@ -13634,21 +13634,21 @@
         <v>67</v>
       </c>
       <c r="AF47" s="3">
-        <f>+AE47+AA47-1</f>
+        <f t="shared" si="30"/>
         <v>102</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
-        <f>+AF47+AG47</f>
+        <f t="shared" si="31"/>
         <v>105</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
       <c r="AJ47" s="3">
-        <f>+AI47+AH47</f>
+        <f t="shared" si="32"/>
         <v>105</v>
       </c>
       <c r="AK47" s="3" t="s">
@@ -13658,36 +13658,36 @@
         <v>10</v>
       </c>
       <c r="AM47" s="3">
-        <f>+AJ47+AL47</f>
+        <f t="shared" si="33"/>
         <v>115</v>
       </c>
       <c r="AN47" s="3">
         <v>3</v>
       </c>
       <c r="AO47" s="3">
-        <f>+AM47+AN47</f>
+        <f t="shared" si="34"/>
         <v>118</v>
       </c>
       <c r="AP47" s="3">
         <v>1</v>
       </c>
       <c r="AQ47" s="3">
-        <f>+AO47+AP47</f>
+        <f t="shared" si="37"/>
         <v>119</v>
       </c>
       <c r="AR47" s="3">
-        <f>+AQ47+7</f>
+        <f t="shared" si="39"/>
         <v>126</v>
       </c>
       <c r="AS47" s="3">
-        <f>+AR47+7+AT47</f>
+        <f t="shared" si="35"/>
         <v>133</v>
       </c>
       <c r="AT47" s="3">
         <v>0</v>
       </c>
       <c r="AU47" s="3">
-        <f>+AA47-R47</f>
+        <f t="shared" si="36"/>
         <v>13</v>
       </c>
       <c r="AV47" s="3" t="s">
@@ -13741,44 +13741,44 @@
         <v>2</v>
       </c>
       <c r="M48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",L48,9)</f>
+        <f t="shared" ref="M48:M53" si="43">+IF(I48="SFK Freight Forwarder",L48,9)</f>
         <v>9</v>
       </c>
       <c r="N48" s="3">
         <v>14</v>
       </c>
       <c r="O48" s="3">
-        <f>IF(I48="SFK Freight Forwarder",M48,M48+N48-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",O48,O48+P48-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f>9+N48</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S48" s="3">
         <v>7</v>
       </c>
       <c r="T48" s="3">
-        <f>+R48+S48-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f>+T48+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V48" s="3">
         <v>1</v>
       </c>
       <c r="W48" s="3">
-        <f>+U48+V48-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X48" s="3">
@@ -13791,7 +13791,7 @@
         <v>37</v>
       </c>
       <c r="AA48" s="6">
-        <f>+Z48+AB48-1</f>
+        <f t="shared" si="42"/>
         <v>39</v>
       </c>
       <c r="AB48" s="3">
@@ -13807,21 +13807,21 @@
         <v>57</v>
       </c>
       <c r="AF48" s="3">
-        <f>+AE48+AA48-1</f>
+        <f t="shared" si="30"/>
         <v>95</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
-        <f>+AF48+AG48</f>
+        <f t="shared" si="31"/>
         <v>98</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
-        <f>+AI48+AH48</f>
+        <f t="shared" si="32"/>
         <v>98</v>
       </c>
       <c r="AK48" s="3" t="s">
@@ -13831,36 +13831,36 @@
         <v>18</v>
       </c>
       <c r="AM48" s="3">
-        <f>+AJ48+AL48</f>
+        <f t="shared" si="33"/>
         <v>116</v>
       </c>
       <c r="AN48" s="3">
         <v>3</v>
       </c>
       <c r="AO48" s="3">
-        <f>+AM48+AN48</f>
+        <f t="shared" si="34"/>
         <v>119</v>
       </c>
       <c r="AP48" s="3">
         <v>0</v>
       </c>
       <c r="AQ48" s="3">
-        <f>+AO48+AP48</f>
+        <f t="shared" si="37"/>
         <v>119</v>
       </c>
       <c r="AR48" s="3">
-        <f>+AQ48+7</f>
+        <f t="shared" si="39"/>
         <v>126</v>
       </c>
       <c r="AS48" s="3">
-        <f>+AR48+7+AT48</f>
+        <f t="shared" si="35"/>
         <v>147</v>
       </c>
       <c r="AT48" s="3">
         <v>14</v>
       </c>
       <c r="AU48" s="3">
-        <f>+AA48-R48</f>
+        <f t="shared" si="36"/>
         <v>16</v>
       </c>
       <c r="AV48" s="3" t="s">
@@ -13914,44 +13914,44 @@
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",L49,9)</f>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="N49" s="3">
         <v>14</v>
       </c>
       <c r="O49" s="3">
-        <f>IF(I49="SFK Freight Forwarder",M49,M49+N49-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",O49,O49+P49-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f>9+N49</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S49" s="3">
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f>+R49+S49-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f>+T49+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V49" s="3">
         <v>1</v>
       </c>
       <c r="W49" s="3">
-        <f>+U49+V49-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X49" s="3">
@@ -13964,7 +13964,7 @@
         <v>37</v>
       </c>
       <c r="AA49" s="6">
-        <f>+Z49+AB49-1</f>
+        <f t="shared" si="42"/>
         <v>38</v>
       </c>
       <c r="AB49" s="3">
@@ -13980,21 +13980,21 @@
         <v>47</v>
       </c>
       <c r="AF49" s="3">
-        <f>+AE49+AA49-1</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AG49" s="6">
         <v>3</v>
       </c>
       <c r="AH49" s="6">
-        <f>+AF49+AG49</f>
+        <f t="shared" si="31"/>
         <v>87</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
-        <f>+AI49+AH49</f>
+        <f t="shared" si="32"/>
         <v>87</v>
       </c>
       <c r="AK49" s="3" t="s">
@@ -14004,36 +14004,36 @@
         <v>16</v>
       </c>
       <c r="AM49" s="3">
-        <f>+AJ49+AL49</f>
+        <f t="shared" si="33"/>
         <v>103</v>
       </c>
       <c r="AN49" s="3">
         <v>2</v>
       </c>
       <c r="AO49" s="3">
-        <f>+AM49+AN49</f>
+        <f t="shared" si="34"/>
         <v>105</v>
       </c>
       <c r="AP49" s="3">
         <v>0</v>
       </c>
       <c r="AQ49" s="3">
-        <f>+AO49+AP49</f>
+        <f t="shared" si="37"/>
         <v>105</v>
       </c>
       <c r="AR49" s="3">
-        <f>+AQ49+7</f>
+        <f t="shared" si="39"/>
         <v>112</v>
       </c>
       <c r="AS49" s="3">
-        <f>+AR49+7+AT49</f>
+        <f t="shared" si="35"/>
         <v>134</v>
       </c>
       <c r="AT49" s="3">
         <v>15</v>
       </c>
       <c r="AU49" s="3">
-        <f>+AA49-R49</f>
+        <f t="shared" si="36"/>
         <v>15</v>
       </c>
       <c r="AV49" s="3" t="s">
@@ -14087,44 +14087,44 @@
         <v>2</v>
       </c>
       <c r="M50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",L50,9)</f>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="N50" s="3">
         <v>14</v>
       </c>
       <c r="O50" s="3">
-        <f>IF(I50="SFK Freight Forwarder",M50,M50+N50-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",O50,O50+P50-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f>9+N50</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S50" s="3">
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f>+R50+S50-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f>+T50+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V50" s="3">
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f>+U50+V50-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X50" s="3">
@@ -14137,7 +14137,7 @@
         <v>36</v>
       </c>
       <c r="AA50" s="6">
-        <f>+Z50+AB50-1</f>
+        <f t="shared" si="42"/>
         <v>37</v>
       </c>
       <c r="AB50" s="3">
@@ -14153,21 +14153,21 @@
         <v>37</v>
       </c>
       <c r="AF50" s="3">
-        <f>+AE50+AA50-1</f>
+        <f t="shared" si="30"/>
         <v>73</v>
       </c>
       <c r="AG50" s="6">
         <v>3</v>
       </c>
       <c r="AH50" s="6">
-        <f>+AF50+AG50</f>
+        <f t="shared" si="31"/>
         <v>76</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
-        <f>+AI50+AH50</f>
+        <f t="shared" si="32"/>
         <v>76</v>
       </c>
       <c r="AK50" s="3" t="s">
@@ -14177,36 +14177,36 @@
         <v>16</v>
       </c>
       <c r="AM50" s="3">
-        <f>+AJ50+AL50</f>
+        <f t="shared" si="33"/>
         <v>92</v>
       </c>
       <c r="AN50" s="3">
         <v>2</v>
       </c>
       <c r="AO50" s="3">
-        <f>+AM50+AN50</f>
+        <f t="shared" si="34"/>
         <v>94</v>
       </c>
       <c r="AP50" s="3">
         <v>4</v>
       </c>
       <c r="AQ50" s="3">
-        <f>+AO50+AP50</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR50" s="3">
-        <f>+AQ50+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS50" s="3">
-        <f>+AR50+7+AT50</f>
+        <f t="shared" si="35"/>
         <v>126</v>
       </c>
       <c r="AT50" s="3">
         <v>14</v>
       </c>
       <c r="AU50" s="3">
-        <f>+AA50-R50</f>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AV50" s="3" t="s">
@@ -14260,44 +14260,44 @@
         <v>7</v>
       </c>
       <c r="M51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",L51,9)</f>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
         <v>14</v>
       </c>
       <c r="O51" s="3">
-        <f>IF(I51="SFK Freight Forwarder",M51,M51+N51-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",O51,O51+P51-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R51" s="3">
-        <f>9+N51</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S51" s="3">
         <v>7</v>
       </c>
       <c r="T51" s="3">
-        <f>+R51+S51-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U51" s="3">
-        <f>+T51+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V51" s="3">
         <v>2</v>
       </c>
       <c r="W51" s="3">
-        <f>+U51+V51-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X51" s="3">
@@ -14310,7 +14310,7 @@
         <v>35</v>
       </c>
       <c r="AA51" s="6">
-        <f>+Z51+AB51-1</f>
+        <f t="shared" si="42"/>
         <v>37</v>
       </c>
       <c r="AB51" s="3">
@@ -14326,21 +14326,21 @@
         <v>36</v>
       </c>
       <c r="AF51" s="3">
-        <f>+AE51+AA51-1</f>
+        <f t="shared" si="30"/>
         <v>72</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
-        <f>+AF51+AG51</f>
+        <f t="shared" si="31"/>
         <v>75</v>
       </c>
       <c r="AI51" s="3">
         <v>0</v>
       </c>
       <c r="AJ51" s="3">
-        <f>+AI51+AH51</f>
+        <f t="shared" si="32"/>
         <v>75</v>
       </c>
       <c r="AK51" s="3" t="s">
@@ -14350,36 +14350,36 @@
         <v>16</v>
       </c>
       <c r="AM51" s="3">
-        <f>+AJ51+AL51</f>
+        <f t="shared" si="33"/>
         <v>91</v>
       </c>
       <c r="AN51" s="3">
         <v>7</v>
       </c>
       <c r="AO51" s="3">
-        <f>+AM51+AN51</f>
+        <f t="shared" si="34"/>
         <v>98</v>
       </c>
       <c r="AP51" s="3">
         <v>0</v>
       </c>
       <c r="AQ51" s="3">
-        <f>+AO51+AP51</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR51" s="3">
-        <f>+AQ51+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS51" s="3">
-        <f>+AR51+7+AT51</f>
+        <f t="shared" si="35"/>
         <v>126</v>
       </c>
       <c r="AT51" s="3">
         <v>14</v>
       </c>
       <c r="AU51" s="3">
-        <f>+AA51-R51</f>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AV51" s="3" t="s">
@@ -14433,44 +14433,44 @@
         <v>7</v>
       </c>
       <c r="M52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",L52,9)</f>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="N52" s="3">
         <v>14</v>
       </c>
       <c r="O52" s="3">
-        <f>IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R52" s="3">
-        <f>9+N52</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S52" s="3">
         <v>7</v>
       </c>
       <c r="T52" s="3">
-        <f>+R52+S52-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U52" s="3">
-        <f>+T52+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V52" s="3">
         <v>2</v>
       </c>
       <c r="W52" s="3">
-        <f>+U52+V52-1</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="X52" s="3">
@@ -14483,7 +14483,7 @@
         <v>33</v>
       </c>
       <c r="AA52" s="6">
-        <f>+Z52+AB52-1</f>
+        <f t="shared" si="42"/>
         <v>35</v>
       </c>
       <c r="AB52" s="3">
@@ -14499,21 +14499,21 @@
         <v>40</v>
       </c>
       <c r="AF52" s="3">
-        <f>+AE52+AA52-1</f>
+        <f t="shared" si="30"/>
         <v>74</v>
       </c>
       <c r="AG52" s="6">
         <v>3</v>
       </c>
       <c r="AH52" s="6">
-        <f>+AF52+AG52</f>
+        <f t="shared" si="31"/>
         <v>77</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
-        <f>+AI52+AH52</f>
+        <f t="shared" si="32"/>
         <v>77</v>
       </c>
       <c r="AK52" s="3" t="s">
@@ -14523,36 +14523,36 @@
         <v>16</v>
       </c>
       <c r="AM52" s="3">
-        <f>+AJ52+AL52</f>
+        <f t="shared" si="33"/>
         <v>93</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
-        <f>+AM52+AN52</f>
+        <f t="shared" si="34"/>
         <v>95</v>
       </c>
       <c r="AP52" s="3">
         <v>3</v>
       </c>
       <c r="AQ52" s="3">
-        <f>+AO52+AP52</f>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AR52" s="3">
-        <f>+AQ52+7</f>
+        <f t="shared" si="39"/>
         <v>105</v>
       </c>
       <c r="AS52" s="3">
-        <f>+AR52+7+AT52</f>
+        <f t="shared" si="35"/>
         <v>126</v>
       </c>
       <c r="AT52" s="3">
         <v>14</v>
       </c>
       <c r="AU52" s="3">
-        <f>+AA52-R52</f>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="AV52" s="3" t="s">
@@ -14606,44 +14606,44 @@
         <v>2</v>
       </c>
       <c r="M53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="N53" s="3">
         <v>14</v>
       </c>
       <c r="O53" s="3">
-        <f>IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="P53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>5</v>
       </c>
       <c r="Q53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
       <c r="R53" s="3">
-        <f>9+N53</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S53" s="3">
         <v>7</v>
       </c>
       <c r="T53" s="3">
-        <f>+R53+S53-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U53" s="3">
-        <f>+T53+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V53" s="3">
         <v>1</v>
       </c>
       <c r="W53" s="3">
-        <f>+U53+V53-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X53" s="3">
@@ -14656,7 +14656,7 @@
         <v>30</v>
       </c>
       <c r="AA53" s="6">
-        <f>+Z53+AB53-1</f>
+        <f t="shared" si="42"/>
         <v>32</v>
       </c>
       <c r="AB53" s="3">
@@ -14672,21 +14672,21 @@
         <v>46</v>
       </c>
       <c r="AF53" s="3">
-        <f>+AE53+AA53-1</f>
+        <f t="shared" si="30"/>
         <v>77</v>
       </c>
       <c r="AG53" s="6">
         <v>3</v>
       </c>
       <c r="AH53" s="6">
-        <f>+AF53+AG53</f>
+        <f t="shared" si="31"/>
         <v>80</v>
       </c>
       <c r="AI53" s="3">
         <v>0</v>
       </c>
       <c r="AJ53" s="3">
-        <f>+AI53+AH53</f>
+        <f t="shared" si="32"/>
         <v>80</v>
       </c>
       <c r="AK53" s="3" t="s">
@@ -14696,36 +14696,36 @@
         <v>18</v>
       </c>
       <c r="AM53" s="3">
-        <f>+AJ53+AL53</f>
+        <f t="shared" si="33"/>
         <v>98</v>
       </c>
       <c r="AN53" s="3">
         <v>3</v>
       </c>
       <c r="AO53" s="3">
-        <f>+AM53+AN53</f>
+        <f t="shared" si="34"/>
         <v>101</v>
       </c>
       <c r="AP53" s="3">
         <v>4</v>
       </c>
       <c r="AQ53" s="3">
-        <f>+AO53+AP53</f>
+        <f t="shared" si="37"/>
         <v>105</v>
       </c>
       <c r="AR53" s="3">
-        <f>+AQ53+7</f>
+        <f t="shared" si="39"/>
         <v>112</v>
       </c>
       <c r="AS53" s="3">
-        <f>+AR53+7+AT53</f>
+        <f t="shared" si="35"/>
         <v>133</v>
       </c>
       <c r="AT53" s="3">
         <v>14</v>
       </c>
       <c r="AU53" s="3">
-        <f>+AA53-R53</f>
+        <f t="shared" si="36"/>
         <v>9</v>
       </c>
       <c r="AV53" s="3" t="s">
@@ -14785,37 +14785,37 @@
         <v>14</v>
       </c>
       <c r="O54" s="3">
-        <f>IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P54" s="3">
-        <f>+IF(I54="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q54" s="3">
-        <f>+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R54" s="3">
-        <f>9+N54</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S54" s="3">
         <v>7</v>
       </c>
       <c r="T54" s="3">
-        <f>+R54+S54-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U54" s="3">
-        <f>+T54+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V54" s="3">
         <v>1</v>
       </c>
       <c r="W54" s="3">
-        <f>+U54+V54-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X54" s="3">
@@ -14828,7 +14828,7 @@
         <v>31</v>
       </c>
       <c r="AA54" s="6">
-        <f>+Z54+AB54-1</f>
+        <f t="shared" si="42"/>
         <v>33</v>
       </c>
       <c r="AB54" s="3">
@@ -14844,21 +14844,21 @@
         <v>34</v>
       </c>
       <c r="AF54" s="3">
-        <f>+AE54+AA54-1</f>
+        <f t="shared" si="30"/>
         <v>66</v>
       </c>
       <c r="AG54" s="6">
         <v>3</v>
       </c>
       <c r="AH54" s="6">
-        <f>+AF54+AG54</f>
+        <f t="shared" si="31"/>
         <v>69</v>
       </c>
       <c r="AI54" s="3">
         <v>0</v>
       </c>
       <c r="AJ54" s="3">
-        <f>+AI54+AH54</f>
+        <f t="shared" si="32"/>
         <v>69</v>
       </c>
       <c r="AK54" s="3" t="s">
@@ -14868,36 +14868,36 @@
         <v>14</v>
       </c>
       <c r="AM54" s="3">
-        <f>+AJ54+AL54</f>
+        <f t="shared" si="33"/>
         <v>83</v>
       </c>
       <c r="AN54" s="3">
         <v>0</v>
       </c>
       <c r="AO54" s="3">
-        <f>+AM54+AN54</f>
+        <f t="shared" si="34"/>
         <v>83</v>
       </c>
       <c r="AP54" s="3">
         <v>1</v>
       </c>
       <c r="AQ54" s="3">
-        <f>+AO54+AP54</f>
+        <f t="shared" si="37"/>
         <v>84</v>
       </c>
       <c r="AR54" s="3">
-        <f>+AQ54+7</f>
+        <f t="shared" si="39"/>
         <v>91</v>
       </c>
       <c r="AS54" s="3">
-        <f>+AR54+7+AT54</f>
+        <f t="shared" si="35"/>
         <v>98</v>
       </c>
       <c r="AT54" s="3">
         <v>0</v>
       </c>
       <c r="AU54" s="3">
-        <f>+AA54-R54</f>
+        <f t="shared" si="36"/>
         <v>10</v>
       </c>
       <c r="AV54" s="3" t="s">
@@ -14957,37 +14957,37 @@
         <v>14</v>
       </c>
       <c r="O55" s="3">
-        <f>IF(I55="SFK Freight Forwarder",M55,M55+N55-1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P55" s="3">
-        <f>+IF(I55="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q55" s="3">
-        <f>+IF(I55="SFK Freight Forwarder",O55,O55+P55-1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R55" s="3">
-        <f>9+N55</f>
+        <f t="shared" si="41"/>
         <v>23</v>
       </c>
       <c r="S55" s="3">
         <v>7</v>
       </c>
       <c r="T55" s="3">
-        <f>+R55+S55-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U55" s="3">
-        <f>+T55+1</f>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="V55" s="3">
         <v>1</v>
       </c>
       <c r="W55" s="3">
-        <f>+U55+V55-1</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="X55" s="3">
@@ -15001,7 +15001,7 @@
         <v>33</v>
       </c>
       <c r="AA55" s="6">
-        <f>+Z55+AB55-1</f>
+        <f t="shared" si="42"/>
         <v>37</v>
       </c>
       <c r="AB55" s="3">
@@ -15017,21 +15017,21 @@
         <v>48</v>
       </c>
       <c r="AF55" s="3">
-        <f>+AE55+AA55-1</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AG55" s="6">
         <v>3</v>
       </c>
       <c r="AH55" s="6">
-        <f>+AF55+AG55</f>
+        <f t="shared" si="31"/>
         <v>87</v>
       </c>
       <c r="AI55" s="3">
         <v>14</v>
       </c>
       <c r="AJ55" s="3">
-        <f>+AI55+AH55</f>
+        <f t="shared" si="32"/>
         <v>101</v>
       </c>
       <c r="AK55" s="3" t="s">
@@ -15041,36 +15041,36 @@
         <v>16</v>
       </c>
       <c r="AM55" s="3">
-        <f>+AJ55+AL55</f>
+        <f t="shared" si="33"/>
         <v>117</v>
       </c>
       <c r="AN55" s="3">
         <v>2</v>
       </c>
       <c r="AO55" s="3">
-        <f>+AM55+AN55</f>
+        <f t="shared" si="34"/>
         <v>119</v>
       </c>
       <c r="AP55" s="3">
         <v>0</v>
       </c>
       <c r="AQ55" s="3">
-        <f>+AO55+AP55</f>
+        <f t="shared" si="37"/>
         <v>119</v>
       </c>
       <c r="AR55" s="3">
-        <f>+AQ55+7</f>
+        <f t="shared" si="39"/>
         <v>126</v>
       </c>
       <c r="AS55" s="3">
-        <f>+AR55+7+AT55</f>
+        <f t="shared" si="35"/>
         <v>133</v>
       </c>
       <c r="AT55" s="3">
         <v>0</v>
       </c>
       <c r="AU55" s="3">
-        <f>+AA55-R55</f>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AV55" s="3" t="s">
@@ -15112,14 +15112,11 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY56" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ROMANIA"/>
+        <filter val="O004"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY56">
-      <sortCondition ref="AI1:AI56"/>
-    </sortState>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Projects\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8930C3-736F-46D2-9935-D44476D6102E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3592DDC9-10F8-4040-80FE-5E2DE67805C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="194" r:id="rId6"/>
+    <pivotCache cacheId="197" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4820,7 +4820,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="194" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="197" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="51">
     <pivotField compact="0" outline="0" showAll="0">
@@ -8010,7 +8010,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>901</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>924</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>932</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>77</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F20" s="19">
         <v>90012500</v>
@@ -11339,7 +11339,7 @@
         <v>5</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q65" si="29">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q55" si="29">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>26</v>
       </c>
       <c r="R34" s="3">
@@ -11390,21 +11390,21 @@
         <v>75</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF65" si="30">+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF55" si="30">+AE34+AA34-1</f>
         <v>109</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH65" si="31">+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH55" si="31">+AF34+AG34</f>
         <v>112</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ65" si="32">+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ55" si="32">+AI34+AH34</f>
         <v>112</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -11414,14 +11414,14 @@
         <v>9</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM65" si="33">+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM55" si="33">+AJ34+AL34</f>
         <v>121</v>
       </c>
       <c r="AN34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO65" si="34">+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO55" si="34">+AM34+AN34</f>
         <v>123</v>
       </c>
       <c r="AP34" s="3">
@@ -11436,7 +11436,7 @@
         <v>133</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS65" si="35">+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS55" si="35">+AR34+7+AT34</f>
         <v>150</v>
       </c>
       <c r="AT34" s="3">
@@ -11600,7 +11600,7 @@
         <v>5</v>
       </c>
       <c r="AQ35" s="3">
-        <f t="shared" ref="AQ35:AQ66" si="37">+AO35+AP35</f>
+        <f t="shared" ref="AQ35:AQ55" si="37">+AO35+AP35</f>
         <v>91</v>
       </c>
       <c r="AR35" s="3">
@@ -12124,7 +12124,7 @@
         <v>84</v>
       </c>
       <c r="AR38" s="3">
-        <f t="shared" ref="AR38:AR69" si="39">+AQ38+7</f>
+        <f t="shared" ref="AR38:AR55" si="39">+AQ38+7</f>
         <v>91</v>
       </c>
       <c r="AS38" s="3">
@@ -15112,18 +15112,18 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY56" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
+    <filterColumn colId="1">
       <filters>
-        <filter val="O004"/>
+        <filter val="ROMANIA"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K12 D67:D1048190 E57:E1048190 C2:E12 C16:E56 C57:C1048190 K16:K1048190" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K12 D67:D1048190 E57:E1048190 C2:E12 K16:K1048190 C57:C1048190 C16:E56" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D67:D1048190 J12:J55 I2:I55 K2:K55 C57:C1048190 H56:K1048190 C2:E56 E57:E1048190" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D67:D1048190 J12:J55 I2:I55 K2:K55 C57:C1048190 H56:K1048190 E57:E1048190 C2:E56" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048190" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Projects\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3592DDC9-10F8-4040-80FE-5E2DE67805C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A84CA6-B8EE-43AE-850E-771BED3D6D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="38700" windowHeight="15345" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="197" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1317,7 +1317,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4820,7 +4820,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="197" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2E0C66C-B4D2-463C-A713-134E1EB62810}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="51">
     <pivotField compact="0" outline="0" showAll="0">
@@ -5612,34 +5612,34 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.453125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.54296875" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.81640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.453125" style="9" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="10.453125" customWidth="1"/>
-    <col min="14" max="14" width="14.54296875" customWidth="1"/>
-    <col min="15" max="34" width="10.453125" customWidth="1"/>
-    <col min="35" max="36" width="15.1796875" customWidth="1"/>
-    <col min="37" max="37" width="15.81640625" customWidth="1"/>
-    <col min="38" max="39" width="9.54296875" customWidth="1"/>
-    <col min="40" max="41" width="15.453125" customWidth="1"/>
-    <col min="42" max="42" width="10.453125" customWidth="1" collapsed="1"/>
-    <col min="43" max="49" width="10.453125" customWidth="1"/>
-    <col min="50" max="50" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="34" width="10.42578125" customWidth="1"/>
+    <col min="35" max="36" width="15.140625" customWidth="1"/>
+    <col min="37" max="37" width="15.85546875" customWidth="1"/>
+    <col min="38" max="39" width="9.5703125" customWidth="1"/>
+    <col min="40" max="41" width="15.42578125" customWidth="1"/>
+    <col min="42" max="42" width="10.42578125" customWidth="1" collapsed="1"/>
+    <col min="43" max="49" width="10.42578125" customWidth="1"/>
+    <col min="50" max="50" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:58" ht="45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" hidden="1">
       <c r="A2" s="5" t="s">
         <v>138</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" hidden="1">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" hidden="1">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" hidden="1">
       <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" hidden="1">
       <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" hidden="1">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" hidden="1">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" hidden="1">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58">
       <c r="A10" s="5" t="s">
         <v>168</v>
       </c>
@@ -7300,19 +7300,19 @@
         <v>83</v>
       </c>
       <c r="AP10" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ10" s="23">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR10" s="23">
         <f t="shared" si="17"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AS10" s="23">
         <f t="shared" si="9"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AT10" s="23">
         <v>14</v>
@@ -7334,7 +7334,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" hidden="1">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" hidden="1">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" hidden="1">
       <c r="A13" s="5">
         <v>233</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" hidden="1">
       <c r="A14" s="5">
         <v>416</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" hidden="1">
       <c r="A15" s="5">
         <v>901</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" hidden="1">
       <c r="A16" s="5">
         <v>907</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" hidden="1">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:51" hidden="1">
       <c r="A18" s="5">
         <v>920</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" hidden="1">
       <c r="A19" s="5">
         <v>924</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" hidden="1">
       <c r="A20" s="5">
         <v>932</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" hidden="1">
       <c r="A21" s="5">
         <v>1039</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" hidden="1">
       <c r="A22" s="5">
         <v>1084</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" hidden="1">
       <c r="A23" s="5">
         <v>752</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" hidden="1">
       <c r="A24" s="5">
         <v>1006</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" hidden="1">
       <c r="A25" s="5">
         <v>1009</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" hidden="1">
       <c r="A26" s="5">
         <v>1010</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" hidden="1">
       <c r="A27" s="5">
         <v>1014</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="5">
         <v>1015</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" hidden="1">
       <c r="A29" s="5">
         <v>1034</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" hidden="1">
       <c r="A30" s="5">
         <v>1036</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" hidden="1">
       <c r="A31" s="5">
         <v>1040</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" hidden="1">
       <c r="A32" s="5">
         <v>60</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" hidden="1">
       <c r="A33" s="5">
         <v>120</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" hidden="1">
       <c r="A34" s="5">
         <v>121</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" hidden="1">
       <c r="A35" s="5">
         <v>908</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" hidden="1">
       <c r="A36" s="5">
         <v>910</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" hidden="1">
       <c r="A37" s="5">
         <v>912</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" hidden="1">
       <c r="A38" s="5">
         <v>916</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" hidden="1">
       <c r="A39" s="5">
         <v>921</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" hidden="1">
       <c r="A40" s="5">
         <v>928</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" hidden="1">
       <c r="A41" s="5">
         <v>930</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" ht="30" hidden="1">
       <c r="A42" s="5">
         <v>931</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" hidden="1">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:51" hidden="1">
       <c r="A44" s="5">
         <v>761</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" hidden="1">
       <c r="A45" s="5">
         <v>888</v>
       </c>
@@ -13357,7 +13357,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1">
       <c r="A46" s="5">
         <v>1007</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" hidden="1">
       <c r="A47" s="5">
         <v>1037</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:51" hidden="1">
       <c r="A48" s="5">
         <v>904</v>
       </c>
@@ -13876,7 +13876,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" hidden="1">
       <c r="A49" s="5">
         <v>906</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1">
       <c r="A50" s="5">
         <v>917</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1">
       <c r="A51" s="5">
         <v>918</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" hidden="1">
       <c r="A52" s="5">
         <v>925</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:51" hidden="1">
       <c r="A53" s="5">
         <v>927</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:51" hidden="1">
       <c r="A54" s="5">
         <v>1005</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:51" hidden="1">
       <c r="A55" s="5">
         <v>1012</v>
       </c>
@@ -15086,35 +15086,35 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="56" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:51" hidden="1">
       <c r="A56" s="49" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:51">
       <c r="D58" s="42"/>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:51">
       <c r="D60" s="41"/>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:51">
       <c r="D62" s="42"/>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:51">
       <c r="D64" s="41"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:4">
       <c r="D65" s="42"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="4:4">
       <c r="D66" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY56" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ROMANIA"/>
+        <filter val="O009"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -15143,9 +15143,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="B2:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5">
       <c r="B2" t="s">
         <v>161</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>164</v>
       </c>
@@ -15173,7 +15173,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>167</v>
       </c>
@@ -15186,15 +15186,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20166134-0068-44E4-897C-A3439A6356AD}">
   <dimension ref="D7:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="4:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:8" ht="30">
       <c r="D7" s="31" t="s">
         <v>6</v>
       </c>
@@ -15211,7 +15211,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="4:8" ht="15.75">
       <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="4:8" ht="15.75">
       <c r="D9" s="43" t="s">
         <v>98</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="10" spans="4:8" ht="15.75">
       <c r="D10" s="43" t="s">
         <v>62</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="4:8" ht="15.75">
       <c r="D11" s="43" t="s">
         <v>68</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="4:8" ht="15.75">
       <c r="D12" s="23" t="s">
         <v>68</v>
       </c>
@@ -15296,7 +15296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="4:8" ht="15.75">
       <c r="D13" s="23" t="s">
         <v>68</v>
       </c>
@@ -15313,7 +15313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="4:8" ht="15.75">
       <c r="D14" s="43" t="s">
         <v>52</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="4:8" ht="15.75">
       <c r="D15" s="23" t="s">
         <v>57</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="16" spans="4:8" ht="15.75">
       <c r="D16" s="43" t="s">
         <v>90</v>
       </c>
@@ -15364,7 +15364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="4:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="4:8" ht="15.75">
       <c r="D17" s="43" t="s">
         <v>96</v>
       </c>
@@ -15401,9 +15401,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D049-164C-47D4-96CD-56CBAA0ABF56}">
   <dimension ref="A1:BF3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:58" ht="45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58">
       <c r="A2" s="5" t="s">
         <v>176</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58">
       <c r="A3" s="5" t="s">
         <v>178</v>
       </c>
@@ -15902,13 +15902,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01200DF6-139A-4B77-AD8A-EBE824C5F285}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="53" t="s">
         <v>129</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="53" t="s">
         <v>6</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -15932,7 +15932,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -15956,7 +15956,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -15972,7 +15972,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -15980,7 +15980,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>98</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -16004,7 +16004,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>182</v>
       </c>
